--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,9 +257,6 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -901,7 +898,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Precificação, uma linha por procedimento: minutos, se gera retorno, material por atendimento, o preço particular que você pratica hoje e a tabela de cada convênio (as mesmas da planilha 08).</t>
+          <t>Em Precificação, uma linha por procedimento: minutos, se gera retorno, material por atendimento, o preço particular que você pratica hoje e a tabela de cada convênio. Copie os valores da planilha 08 · Tabela de preços: ela é a fonte única da tabela no kit (a 07 e a Config da 01 também copiam de lá).</t>
         </is>
       </c>
     </row>
@@ -925,7 +922,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Revise quando o custo-hora mudar (05) ou uma vez por semestre. Depois de decidir, atualize a tabela de preços (08) e a Config da agenda (01).</t>
+          <t>Revise quando o custo-hora mudar (05) ou uma vez por semestre. Decidiu mudar um preço? Atualize na ordem: 08 (tabela de preços, a fonte) → 06 (esta) → 07 (simulador) → 01 (Config da agenda). Assim os quatro arquivos continuam com o mesmo número.</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1148,33 @@
         <f>IF(Config!$B$15="","",Config!$B$15)</f>
         <v>Saúde Total</v>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
+      <c r="M4" s="7" t="str">
+        <f>IF(Config!$B$15="","","Margem")</f>
+        <v>Margem</v>
       </c>
       <c r="N4" s="7" t="str">
         <f>IF(Config!$B$16="","",Config!$B$16)</f>
         <v>MediPlan</v>
       </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
+      <c r="O4" s="7" t="str">
+        <f>IF(Config!$B$16="","","Margem")</f>
+        <v>Margem</v>
       </c>
       <c r="P4" s="7" t="str">
         <f>IF(Config!$B$17="","",Config!$B$17)</f>
         <v>Vida Care</v>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
+      <c r="Q4" s="7" t="str">
+        <f>IF(Config!$B$17="","","Margem")</f>
+        <v>Margem</v>
       </c>
       <c r="R4" s="7">
         <f>IF(Config!$B$18="","",Config!$B$18)</f>
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
+      <c r="S4" s="7">
+        <f>IF(Config!$B$18="","","Margem")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1225,7 +1218,7 @@
         <v>0.546140350877193</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IF(J5="","",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A5="",I5=""),"",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L5" s="15" t="n">
@@ -1311,9 +1304,9 @@
         <f>IF(OR(A6="",I6="",I6=0),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
         <v/>
       </c>
-      <c r="K6" s="17">
-        <f>IF(J6="","",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima")))</f>
-        <v/>
+      <c r="K6" s="17" t="str">
+        <f>IF(OR(A6="",I6=""),"",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <v>Sem cobrança</v>
       </c>
       <c r="L6" s="15" t="n">
         <v>0</v>
@@ -1399,7 +1392,7 @@
         <v>0.315641025641026</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IF(J7="","",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A7="",I7=""),"",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="L7" s="15" t="n">
@@ -1486,7 +1479,7 @@
         <v>0.617777777777778</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IF(J8="","",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A8="",I8=""),"",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L8" s="15" t="n">
@@ -1573,7 +1566,7 @@
         <v>0.648095238095238</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IF(J9="","",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A9="",I9=""),"",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L9" s="15" t="n">
@@ -1660,7 +1653,7 @@
         <v>0.538148148148148</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IF(J10="","",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A10="",I10=""),"",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L10" s="15" t="n">
@@ -1747,7 +1740,7 @@
         <v>0.48</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IF(J11="","",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A11="",I11=""),"",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L11" s="15" t="n">
@@ -1816,7 +1809,7 @@
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF(J12="","",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A12="",I12=""),"",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -1883,7 +1876,7 @@
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF(J13="","",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A13="",I13=""),"",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
       <c r="L13" s="15" t="n"/>
@@ -1950,7 +1943,7 @@
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF(J14="","",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A14="",I14=""),"",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
       <c r="L14" s="15" t="n"/>
@@ -2017,7 +2010,7 @@
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF(J15="","",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A15="",I15=""),"",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
       <c r="L15" s="15" t="n"/>
@@ -2084,7 +2077,7 @@
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF(J16="","",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima")))</f>
+        <f>IF(OR(A16="",I16=""),"",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
       <c r="L16" s="15" t="n"/>
@@ -2192,7 +2185,7 @@
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
-          <t>Tabelas de convênio que não cobrem o custo cheio</t>
+          <t>Tabelas de convênio abaixo do custo cheio + imposto</t>
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
@@ -2217,10 +2210,10 @@
         <v>60.4333333333333</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>"Maior prejuízo" = margem negativa × tabela do convênio: a célula mais vermelha da tabela, em reais por atendimento (colunas auxiliares T a W, ocultas).</t>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>"Abaixo do custo cheio + imposto" conta as células de Margem negativas: a tabela do convênio, depois dos impostos, não paga o custo cheio do atendimento. É a mesma conta e o mesmo número do KPI "Tabelas de convênio abaixo do custo cheio + imposto" da planilha 08. "Maior prejuízo" = margem negativa × tabela do convênio: a célula mais vermelha da tabela, em reais por atendimento (colunas auxiliares T a W, ocultas).</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2226,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
@@ -2245,7 +2238,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
@@ -2255,7 +2248,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Gera retorno? (Sim/Não)</t>
         </is>
@@ -2267,7 +2260,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>Material (R$)</t>
         </is>
@@ -2277,7 +2270,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Preço pretendido (R$)</t>
         </is>
@@ -2303,7 +2296,7 @@
           <t>Custo cheio (R$)</t>
         </is>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <f>B35/60*Config!$B$7+B33</f>
         <v>180.666666666667</v>
       </c>
@@ -2325,7 +2318,7 @@
           <t>Preço alvo (R$)</t>
         </is>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <f>IFERROR(B36/(1-Config!$B$8-Config!$B$10),"")</f>
         <v>410.606060606061</v>
       </c>
@@ -2347,7 +2340,7 @@
           <t>Leitura</t>
         </is>
       </c>
-      <c r="B40" s="29" t="str">
+      <c r="B40" s="28" t="str">
         <f>IF(B34=0,"",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))</f>
         <v>No alvo ou acima</v>
       </c>
@@ -2363,10 +2356,10 @@
     <mergeCell ref="A19:S19"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A18:S18"/>
+    <mergeCell ref="A27:S27"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A1:R1"/>
@@ -2481,7 +2474,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Nome da clínica</t>
         </is>
@@ -2493,7 +2486,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Mês de referência</t>
         </is>
@@ -2505,18 +2498,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <f>TODAY()</f>
         <v>46279.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento (R$)</t>
         </is>
@@ -2524,74 +2517,74 @@
       <c r="B7" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Copie do Painel da planilha 05 ("Custo da hora de atendimento"). No exemplo, R$ 200,00 (R$ 28.000 ÷ 140 h).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>Impostos e taxas sobre o que entra (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="n">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Impostos sobre o que entra (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>A mesma alíquota efetiva da planilha 05 (exemplo: 11 %; confira com o contador).</t>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>A mesma alíquota efetiva da planilha 05 (exemplo: 11 %; confira com o contador). Só imposto: a taxa da maquininha não entra aqui (ela está na 16 e no resultado 18).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Margem mínima sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>Abaixo disso o procedimento não vale a pena. É o piso da faixa (a mesma margem da 05).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Margem alvo sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>A margem que a clínica quer de verdade. É o teto da faixa.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Retornos por consulta (média)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>Consulta que costuma gerar retorno sem cobrança: em média, quantos retornos por consulta. O tempo do retorno entra no custo da consulta.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Duração do retorno (minutos)</t>
         </is>
@@ -2599,21 +2592,21 @@
       <c r="B12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>Minutos de um retorno (planilha 01, Config).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Convênios (até 4, na ordem das colunas da aba Precificação)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Nomes</t>
         </is>
@@ -2623,7 +2616,7 @@
           <t>Saúde Total</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>Preencha de cima para baixo, sem pular linha. As tabelas de cada convênio ficam na aba Precificação.</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -219,20 +220,20 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -259,14 +260,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -845,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1018,17 +1019,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2503,9 +2516,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="30">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B6" s="30" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="7">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2395,10 +2395,10 @@
       <formula>AND(ISNUMBER(J5),J5&lt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>AND(ISNUMBER(J5),J5&gt;=0,J5&lt;Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(J5),J5&gt;=0,J5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="2">
-      <formula>AND(ISNUMBER(J5),J5&gt;=Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(J5),J5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M16">
@@ -2406,10 +2406,10 @@
       <formula>AND(ISNUMBER(M5),M5&lt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="1">
-      <formula>AND(ISNUMBER(M5),M5&gt;=0,M5&lt;Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(M5),M5&gt;=0,M5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="2">
-      <formula>AND(ISNUMBER(M5),M5&gt;=Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(M5),M5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O16">
@@ -2417,10 +2417,10 @@
       <formula>AND(ISNUMBER(O5),O5&lt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="1">
-      <formula>AND(ISNUMBER(O5),O5&gt;=0,O5&lt;Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(O5),O5&gt;=0,O5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="2">
-      <formula>AND(ISNUMBER(O5),O5&gt;=Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(O5),O5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q16">
@@ -2428,10 +2428,10 @@
       <formula>AND(ISNUMBER(Q5),Q5&lt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="1">
-      <formula>AND(ISNUMBER(Q5),Q5&gt;=0,Q5&lt;Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(Q5),Q5&gt;=0,Q5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="2">
-      <formula>AND(ISNUMBER(Q5),Q5&gt;=Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(Q5),Q5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S16">
@@ -2439,10 +2439,10 @@
       <formula>AND(ISNUMBER(S5),S5&lt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="17" dxfId="1">
-      <formula>AND(ISNUMBER(S5),S5&gt;=0,S5&lt;Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(S5),S5&gt;=0,S5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
     <cfRule type="expression" priority="18" dxfId="2">
-      <formula>AND(ISNUMBER(S5),S5&gt;=Config!$B$9)</formula>
+      <formula>AND(ISNUMBER(S5),S5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1212,52 +1212,52 @@
         <v>38</v>
       </c>
       <c r="F5" s="13">
-        <f>IF(A5="","",E5/60*Config!$B$7+D5)</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E5/60*Config!$B$7+D5))</f>
         <v>130.666666666667</v>
       </c>
       <c r="G5" s="14">
-        <f>IF(A5="","",IFERROR(F5/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(F5)),F5,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F5/(1-Config!$B$8-Config!$B$9))))</f>
         <v>221.468926553672</v>
       </c>
       <c r="H5" s="13">
-        <f>IF(A5="","",IFERROR(F5/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(F5)),F5,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F5/(1-Config!$B$8-Config!$B$10))))</f>
         <v>296.969696969697</v>
       </c>
       <c r="I5" s="15" t="n">
         <v>380</v>
       </c>
       <c r="J5" s="16">
-        <f>IF(OR(A5="",I5="",I5=0),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
+        <f>IF(OR(A5="",I5="",I5=0,NOT(ISNUMBER(F5))),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
         <v>0.546140350877193</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IF(OR(A5="",I5=""),"",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A5="",I5=""),"",IF(NOT(ISNUMBER(F5)),"Falta o custo-hora",IF(NOT(ISNUMBER(G5)),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L5" s="15" t="n">
         <v>120</v>
       </c>
       <c r="M5" s="16">
-        <f>IF(OR(A5="",L5="",L5=0),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
+        <f>IF(OR(A5="",L5="",L5=0,NOT(ISNUMBER(F5))),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>100</v>
       </c>
       <c r="O5" s="16">
-        <f>IF(OR(A5="",N5="",N5=0),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
+        <f>IF(OR(A5="",N5="",N5=0,NOT(ISNUMBER(F5))),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
         <v>-0.416666666666667</v>
       </c>
       <c r="P5" s="15" t="n">
         <v>90</v>
       </c>
       <c r="Q5" s="16">
-        <f>IF(OR(A5="",P5="",P5=0),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
+        <f>IF(OR(A5="",P5="",P5=0,NOT(ISNUMBER(F5))),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
         <v>-0.561851851851852</v>
       </c>
       <c r="R5" s="15" t="n"/>
       <c r="S5" s="16">
-        <f>IF(OR(A5="",R5="",R5=0),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
+        <f>IF(OR(A5="",R5="",R5=0,NOT(ISNUMBER(F5))),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
         <v/>
       </c>
       <c r="T5" s="18">
@@ -1299,52 +1299,52 @@
         <v>20</v>
       </c>
       <c r="F6" s="13">
-        <f>IF(A6="","",E6/60*Config!$B$7+D6)</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E6/60*Config!$B$7+D6))</f>
         <v>68.6666666666667</v>
       </c>
       <c r="G6" s="14">
-        <f>IF(A6="","",IFERROR(F6/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(F6)),F6,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F6/(1-Config!$B$8-Config!$B$9))))</f>
         <v>116.38418079096</v>
       </c>
       <c r="H6" s="13">
-        <f>IF(A6="","",IFERROR(F6/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(F6)),F6,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F6/(1-Config!$B$8-Config!$B$10))))</f>
         <v>156.060606060606</v>
       </c>
       <c r="I6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="16">
-        <f>IF(OR(A6="",I6="",I6=0),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
+        <f>IF(OR(A6="",I6="",I6=0,NOT(ISNUMBER(F6))),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
         <v/>
       </c>
       <c r="K6" s="17" t="str">
-        <f>IF(OR(A6="",I6=""),"",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A6="",I6=""),"",IF(NOT(ISNUMBER(F6)),"Falta o custo-hora",IF(NOT(ISNUMBER(G6)),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="L6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f>IF(OR(A6="",L6="",L6=0),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
+        <f>IF(OR(A6="",L6="",L6=0,NOT(ISNUMBER(F6))),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
         <v/>
       </c>
       <c r="N6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="16">
-        <f>IF(OR(A6="",N6="",N6=0),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
+        <f>IF(OR(A6="",N6="",N6=0,NOT(ISNUMBER(F6))),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
         <v/>
       </c>
       <c r="P6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="16">
-        <f>IF(OR(A6="",P6="",P6=0),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
+        <f>IF(OR(A6="",P6="",P6=0,NOT(ISNUMBER(F6))),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
         <v/>
       </c>
       <c r="R6" s="15" t="n"/>
       <c r="S6" s="16">
-        <f>IF(OR(A6="",R6="",R6=0),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
+        <f>IF(OR(A6="",R6="",R6=0,NOT(ISNUMBER(F6))),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
         <v/>
       </c>
       <c r="T6" s="18">
@@ -1386,52 +1386,52 @@
         <v>20</v>
       </c>
       <c r="F7" s="13">
-        <f>IF(A7="","",E7/60*Config!$B$7+D7)</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E7/60*Config!$B$7+D7))</f>
         <v>74.6666666666667</v>
       </c>
       <c r="G7" s="14">
-        <f>IF(A7="","",IFERROR(F7/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(F7)),F7,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F7/(1-Config!$B$8-Config!$B$9))))</f>
         <v>126.553672316384</v>
       </c>
       <c r="H7" s="13">
-        <f>IF(A7="","",IFERROR(F7/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(F7)),F7,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F7/(1-Config!$B$8-Config!$B$10))))</f>
         <v>169.69696969697</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>130</v>
       </c>
       <c r="J7" s="16">
-        <f>IF(OR(A7="",I7="",I7=0),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
+        <f>IF(OR(A7="",I7="",I7=0,NOT(ISNUMBER(F7))),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
         <v>0.315641025641026</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IF(OR(A7="",I7=""),"",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A7="",I7=""),"",IF(NOT(ISNUMBER(F7)),"Falta o custo-hora",IF(NOT(ISNUMBER(G7)),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="L7" s="15" t="n">
         <v>40</v>
       </c>
       <c r="M7" s="16">
-        <f>IF(OR(A7="",L7="",L7=0),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
+        <f>IF(OR(A7="",L7="",L7=0,NOT(ISNUMBER(F7))),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
         <v>-0.976666666666666</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>35</v>
       </c>
       <c r="O7" s="16">
-        <f>IF(OR(A7="",N7="",N7=0),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
+        <f>IF(OR(A7="",N7="",N7=0,NOT(ISNUMBER(F7))),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
         <v>-1.24333333333333</v>
       </c>
       <c r="P7" s="15" t="n">
         <v>32</v>
       </c>
       <c r="Q7" s="16">
-        <f>IF(OR(A7="",P7="",P7=0),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
+        <f>IF(OR(A7="",P7="",P7=0,NOT(ISNUMBER(F7))),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
         <v>-1.44333333333333</v>
       </c>
       <c r="R7" s="15" t="n"/>
       <c r="S7" s="16">
-        <f>IF(OR(A7="",R7="",R7=0),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
+        <f>IF(OR(A7="",R7="",R7=0,NOT(ISNUMBER(F7))),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
         <v/>
       </c>
       <c r="T7" s="18">
@@ -1473,52 +1473,52 @@
         <v>20</v>
       </c>
       <c r="F8" s="13">
-        <f>IF(A8="","",E8/60*Config!$B$7+D8)</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E8/60*Config!$B$7+D8))</f>
         <v>81.6666666666667</v>
       </c>
       <c r="G8" s="14">
-        <f>IF(A8="","",IFERROR(F8/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(F8)),F8,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F8/(1-Config!$B$8-Config!$B$9))))</f>
         <v>138.418079096045</v>
       </c>
       <c r="H8" s="13">
-        <f>IF(A8="","",IFERROR(F8/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(F8)),F8,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F8/(1-Config!$B$8-Config!$B$10))))</f>
         <v>185.606060606061</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>300</v>
       </c>
       <c r="J8" s="16">
-        <f>IF(OR(A8="",I8="",I8=0),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
+        <f>IF(OR(A8="",I8="",I8=0,NOT(ISNUMBER(F8))),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
         <v>0.617777777777778</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IF(OR(A8="",I8=""),"",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A8="",I8=""),"",IF(NOT(ISNUMBER(F8)),"Falta o custo-hora",IF(NOT(ISNUMBER(G8)),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L8" s="15" t="n">
         <v>95</v>
       </c>
       <c r="M8" s="16">
-        <f>IF(OR(A8="",L8="",L8=0),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
+        <f>IF(OR(A8="",L8="",L8=0,NOT(ISNUMBER(F8))),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
         <v>0.0303508771929825</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>85</v>
       </c>
       <c r="O8" s="16">
-        <f>IF(OR(A8="",N8="",N8=0),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
+        <f>IF(OR(A8="",N8="",N8=0,NOT(ISNUMBER(F8))),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
         <v>-0.07078431372549</v>
       </c>
       <c r="P8" s="15" t="n">
         <v>75</v>
       </c>
       <c r="Q8" s="16">
-        <f>IF(OR(A8="",P8="",P8=0),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
+        <f>IF(OR(A8="",P8="",P8=0,NOT(ISNUMBER(F8))),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="R8" s="15" t="n"/>
       <c r="S8" s="16">
-        <f>IF(OR(A8="",R8="",R8=0),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
+        <f>IF(OR(A8="",R8="",R8=0,NOT(ISNUMBER(F8))),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
         <v/>
       </c>
       <c r="T8" s="18">
@@ -1560,52 +1560,52 @@
         <v>20</v>
       </c>
       <c r="F9" s="13">
-        <f>IF(A9="","",E9/60*Config!$B$7+D9)</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E9/60*Config!$B$7+D9))</f>
         <v>84.6666666666667</v>
       </c>
       <c r="G9" s="14">
-        <f>IF(A9="","",IFERROR(F9/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(F9)),F9,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F9/(1-Config!$B$8-Config!$B$9))))</f>
         <v>143.502824858757</v>
       </c>
       <c r="H9" s="13">
-        <f>IF(A9="","",IFERROR(F9/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(F9)),F9,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F9/(1-Config!$B$8-Config!$B$10))))</f>
         <v>192.424242424242</v>
       </c>
       <c r="I9" s="15" t="n">
         <v>350</v>
       </c>
       <c r="J9" s="16">
-        <f>IF(OR(A9="",I9="",I9=0),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
+        <f>IF(OR(A9="",I9="",I9=0,NOT(ISNUMBER(F9))),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
         <v>0.648095238095238</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IF(OR(A9="",I9=""),"",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A9="",I9=""),"",IF(NOT(ISNUMBER(F9)),"Falta o custo-hora",IF(NOT(ISNUMBER(G9)),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L9" s="15" t="n">
         <v>105</v>
       </c>
       <c r="M9" s="16">
-        <f>IF(OR(A9="",L9="",L9=0),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
+        <f>IF(OR(A9="",L9="",L9=0,NOT(ISNUMBER(F9))),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
         <v>0.0836507936507938</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>95</v>
       </c>
       <c r="O9" s="16">
-        <f>IF(OR(A9="",N9="",N9=0),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
+        <f>IF(OR(A9="",N9="",N9=0,NOT(ISNUMBER(F9))),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
         <v>-0.00122807017543853</v>
       </c>
       <c r="P9" s="15" t="n">
         <v>85</v>
       </c>
       <c r="Q9" s="16">
-        <f>IF(OR(A9="",P9="",P9=0),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
+        <f>IF(OR(A9="",P9="",P9=0,NOT(ISNUMBER(F9))),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
         <v>-0.106078431372549</v>
       </c>
       <c r="R9" s="15" t="n"/>
       <c r="S9" s="16">
-        <f>IF(OR(A9="",R9="",R9=0),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
+        <f>IF(OR(A9="",R9="",R9=0,NOT(ISNUMBER(F9))),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
         <v/>
       </c>
       <c r="T9" s="18">
@@ -1647,52 +1647,52 @@
         <v>40</v>
       </c>
       <c r="F10" s="13">
-        <f>IF(A10="","",E10/60*Config!$B$7+D10)</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E10/60*Config!$B$7+D10))</f>
         <v>158.333333333333</v>
       </c>
       <c r="G10" s="14">
-        <f>IF(A10="","",IFERROR(F10/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(F10)),F10,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F10/(1-Config!$B$8-Config!$B$9))))</f>
         <v>268.361581920904</v>
       </c>
       <c r="H10" s="13">
-        <f>IF(A10="","",IFERROR(F10/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(F10)),F10,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F10/(1-Config!$B$8-Config!$B$10))))</f>
         <v>359.848484848485</v>
       </c>
       <c r="I10" s="15" t="n">
         <v>450</v>
       </c>
       <c r="J10" s="16">
-        <f>IF(OR(A10="",I10="",I10=0),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
+        <f>IF(OR(A10="",I10="",I10=0,NOT(ISNUMBER(F10))),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
         <v>0.538148148148148</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IF(OR(A10="",I10=""),"",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A10="",I10=""),"",IF(NOT(ISNUMBER(F10)),"Falta o custo-hora",IF(NOT(ISNUMBER(G10)),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>140</v>
       </c>
       <c r="M10" s="16">
-        <f>IF(OR(A10="",L10="",L10=0),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
+        <f>IF(OR(A10="",L10="",L10=0,NOT(ISNUMBER(F10))),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
         <v>-0.240952380952381</v>
       </c>
       <c r="N10" s="15" t="n">
         <v>125</v>
       </c>
       <c r="O10" s="16">
-        <f>IF(OR(A10="",N10="",N10=0),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
+        <f>IF(OR(A10="",N10="",N10=0,NOT(ISNUMBER(F10))),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
         <v>-0.376666666666667</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>110</v>
       </c>
       <c r="Q10" s="16">
-        <f>IF(OR(A10="",P10="",P10=0),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
+        <f>IF(OR(A10="",P10="",P10=0,NOT(ISNUMBER(F10))),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
         <v>-0.549393939393939</v>
       </c>
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="16">
-        <f>IF(OR(A10="",R10="",R10=0),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
+        <f>IF(OR(A10="",R10="",R10=0,NOT(ISNUMBER(F10))),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
         <v/>
       </c>
       <c r="T10" s="18">
@@ -1734,48 +1734,48 @@
         <v>48</v>
       </c>
       <c r="F11" s="13">
-        <f>IF(A11="","",E11/60*Config!$B$7+D11)</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E11/60*Config!$B$7+D11))</f>
         <v>164</v>
       </c>
       <c r="G11" s="14">
-        <f>IF(A11="","",IFERROR(F11/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(F11)),F11,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F11/(1-Config!$B$8-Config!$B$9))))</f>
         <v>277.966101694915</v>
       </c>
       <c r="H11" s="13">
-        <f>IF(A11="","",IFERROR(F11/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(F11)),F11,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F11/(1-Config!$B$8-Config!$B$10))))</f>
         <v>372.727272727273</v>
       </c>
       <c r="I11" s="15" t="n">
         <v>400</v>
       </c>
       <c r="J11" s="16">
-        <f>IF(OR(A11="",I11="",I11=0),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
+        <f>IF(OR(A11="",I11="",I11=0,NOT(ISNUMBER(F11))),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
         <v>0.48</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IF(OR(A11="",I11=""),"",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A11="",I11=""),"",IF(NOT(ISNUMBER(F11)),"Falta o custo-hora",IF(NOT(ISNUMBER(G11)),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L11" s="15" t="n">
         <v>130</v>
       </c>
       <c r="M11" s="16">
-        <f>IF(OR(A11="",L11="",L11=0),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
+        <f>IF(OR(A11="",L11="",L11=0,NOT(ISNUMBER(F11))),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
         <v>-0.371538461538462</v>
       </c>
       <c r="N11" s="15" t="n"/>
       <c r="O11" s="16">
-        <f>IF(OR(A11="",N11="",N11=0),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
+        <f>IF(OR(A11="",N11="",N11=0,NOT(ISNUMBER(F11))),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
         <v/>
       </c>
       <c r="P11" s="15" t="n"/>
       <c r="Q11" s="16">
-        <f>IF(OR(A11="",P11="",P11=0),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
+        <f>IF(OR(A11="",P11="",P11=0,NOT(ISNUMBER(F11))),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
         <v/>
       </c>
       <c r="R11" s="15" t="n"/>
       <c r="S11" s="16">
-        <f>IF(OR(A11="",R11="",R11=0),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
+        <f>IF(OR(A11="",R11="",R11=0,NOT(ISNUMBER(F11))),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
         <v/>
       </c>
       <c r="T11" s="18">
@@ -1805,44 +1805,44 @@
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>IF(A12="","",E12/60*Config!$B$7+D12)</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E12/60*Config!$B$7+D12))</f>
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>IF(A12="","",IFERROR(F12/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(F12)),F12,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F12/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>IF(A12="","",IFERROR(F12/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(F12)),F12,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F12/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="16">
-        <f>IF(OR(A12="",I12="",I12=0),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
+        <f>IF(OR(A12="",I12="",I12=0,NOT(ISNUMBER(F12))),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF(OR(A12="",I12=""),"",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A12="",I12=""),"",IF(NOT(ISNUMBER(F12)),"Falta o custo-hora",IF(NOT(ISNUMBER(G12)),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="16">
-        <f>IF(OR(A12="",L12="",L12=0),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
+        <f>IF(OR(A12="",L12="",L12=0,NOT(ISNUMBER(F12))),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
         <v/>
       </c>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="16">
-        <f>IF(OR(A12="",N12="",N12=0),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
+        <f>IF(OR(A12="",N12="",N12=0,NOT(ISNUMBER(F12))),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
         <v/>
       </c>
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="16">
-        <f>IF(OR(A12="",P12="",P12=0),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
+        <f>IF(OR(A12="",P12="",P12=0,NOT(ISNUMBER(F12))),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
         <v/>
       </c>
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="16">
-        <f>IF(OR(A12="",R12="",R12=0),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
+        <f>IF(OR(A12="",R12="",R12=0,NOT(ISNUMBER(F12))),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
         <v/>
       </c>
       <c r="T12" s="18">
@@ -1872,44 +1872,44 @@
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>IF(A13="","",E13/60*Config!$B$7+D13)</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E13/60*Config!$B$7+D13))</f>
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>IF(A13="","",IFERROR(F13/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(F13)),F13,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F13/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>IF(A13="","",IFERROR(F13/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(F13)),F13,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F13/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I13" s="15" t="n"/>
       <c r="J13" s="16">
-        <f>IF(OR(A13="",I13="",I13=0),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
+        <f>IF(OR(A13="",I13="",I13=0,NOT(ISNUMBER(F13))),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF(OR(A13="",I13=""),"",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A13="",I13=""),"",IF(NOT(ISNUMBER(F13)),"Falta o custo-hora",IF(NOT(ISNUMBER(G13)),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="16">
-        <f>IF(OR(A13="",L13="",L13=0),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
+        <f>IF(OR(A13="",L13="",L13=0,NOT(ISNUMBER(F13))),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
         <v/>
       </c>
       <c r="N13" s="15" t="n"/>
       <c r="O13" s="16">
-        <f>IF(OR(A13="",N13="",N13=0),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
+        <f>IF(OR(A13="",N13="",N13=0,NOT(ISNUMBER(F13))),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
         <v/>
       </c>
       <c r="P13" s="15" t="n"/>
       <c r="Q13" s="16">
-        <f>IF(OR(A13="",P13="",P13=0),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
+        <f>IF(OR(A13="",P13="",P13=0,NOT(ISNUMBER(F13))),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
         <v/>
       </c>
       <c r="R13" s="15" t="n"/>
       <c r="S13" s="16">
-        <f>IF(OR(A13="",R13="",R13=0),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
+        <f>IF(OR(A13="",R13="",R13=0,NOT(ISNUMBER(F13))),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
         <v/>
       </c>
       <c r="T13" s="18">
@@ -1939,44 +1939,44 @@
         <v/>
       </c>
       <c r="F14" s="13">
-        <f>IF(A14="","",E14/60*Config!$B$7+D14)</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E14/60*Config!$B$7+D14))</f>
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>IF(A14="","",IFERROR(F14/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(F14)),F14,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F14/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H14" s="13">
-        <f>IF(A14="","",IFERROR(F14/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(F14)),F14,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F14/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I14" s="15" t="n"/>
       <c r="J14" s="16">
-        <f>IF(OR(A14="",I14="",I14=0),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
+        <f>IF(OR(A14="",I14="",I14=0,NOT(ISNUMBER(F14))),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF(OR(A14="",I14=""),"",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A14="",I14=""),"",IF(NOT(ISNUMBER(F14)),"Falta o custo-hora",IF(NOT(ISNUMBER(G14)),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="16">
-        <f>IF(OR(A14="",L14="",L14=0),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
+        <f>IF(OR(A14="",L14="",L14=0,NOT(ISNUMBER(F14))),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
         <v/>
       </c>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="16">
-        <f>IF(OR(A14="",N14="",N14=0),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
+        <f>IF(OR(A14="",N14="",N14=0,NOT(ISNUMBER(F14))),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
         <v/>
       </c>
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="16">
-        <f>IF(OR(A14="",P14="",P14=0),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
+        <f>IF(OR(A14="",P14="",P14=0,NOT(ISNUMBER(F14))),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
         <v/>
       </c>
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="16">
-        <f>IF(OR(A14="",R14="",R14=0),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
+        <f>IF(OR(A14="",R14="",R14=0,NOT(ISNUMBER(F14))),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
         <v/>
       </c>
       <c r="T14" s="18">
@@ -2006,44 +2006,44 @@
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>IF(A15="","",E15/60*Config!$B$7+D15)</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E15/60*Config!$B$7+D15))</f>
         <v/>
       </c>
       <c r="G15" s="14">
-        <f>IF(A15="","",IFERROR(F15/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(F15)),F15,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F15/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>IF(A15="","",IFERROR(F15/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(F15)),F15,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F15/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="16">
-        <f>IF(OR(A15="",I15="",I15=0),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
+        <f>IF(OR(A15="",I15="",I15=0,NOT(ISNUMBER(F15))),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF(OR(A15="",I15=""),"",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A15="",I15=""),"",IF(NOT(ISNUMBER(F15)),"Falta o custo-hora",IF(NOT(ISNUMBER(G15)),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="16">
-        <f>IF(OR(A15="",L15="",L15=0),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
+        <f>IF(OR(A15="",L15="",L15=0,NOT(ISNUMBER(F15))),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
         <v/>
       </c>
       <c r="N15" s="15" t="n"/>
       <c r="O15" s="16">
-        <f>IF(OR(A15="",N15="",N15=0),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
+        <f>IF(OR(A15="",N15="",N15=0,NOT(ISNUMBER(F15))),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
         <v/>
       </c>
       <c r="P15" s="15" t="n"/>
       <c r="Q15" s="16">
-        <f>IF(OR(A15="",P15="",P15=0),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
+        <f>IF(OR(A15="",P15="",P15=0,NOT(ISNUMBER(F15))),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
         <v/>
       </c>
       <c r="R15" s="15" t="n"/>
       <c r="S15" s="16">
-        <f>IF(OR(A15="",R15="",R15=0),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
+        <f>IF(OR(A15="",R15="",R15=0,NOT(ISNUMBER(F15))),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
         <v/>
       </c>
       <c r="T15" s="18">
@@ -2073,44 +2073,44 @@
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>IF(A16="","",E16/60*Config!$B$7+D16)</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E16/60*Config!$B$7+D16))</f>
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>IF(A16="","",IFERROR(F16/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(F16)),F16,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F16/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H16" s="13">
-        <f>IF(A16="","",IFERROR(F16/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(F16)),F16,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F16/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="16">
-        <f>IF(OR(A16="",I16="",I16=0),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
+        <f>IF(OR(A16="",I16="",I16=0,NOT(ISNUMBER(F16))),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF(OR(A16="",I16=""),"",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A16="",I16=""),"",IF(NOT(ISNUMBER(F16)),"Falta o custo-hora",IF(NOT(ISNUMBER(G16)),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="16">
-        <f>IF(OR(A16="",L16="",L16=0),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
+        <f>IF(OR(A16="",L16="",L16=0,NOT(ISNUMBER(F16))),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
         <v/>
       </c>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="16">
-        <f>IF(OR(A16="",N16="",N16=0),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
+        <f>IF(OR(A16="",N16="",N16=0,NOT(ISNUMBER(F16))),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
         <v/>
       </c>
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="16">
-        <f>IF(OR(A16="",P16="",P16=0),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
+        <f>IF(OR(A16="",P16="",P16=0,NOT(ISNUMBER(F16))),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
         <v/>
       </c>
       <c r="R16" s="15" t="n"/>
       <c r="S16" s="16">
-        <f>IF(OR(A16="",R16="",R16=0),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
+        <f>IF(OR(A16="",R16="",R16=0,NOT(ISNUMBER(F16))),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
         <v/>
       </c>
       <c r="T16" s="18">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="B36" s="27">
-        <f>B35/60*Config!$B$7+B33</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",B35/60*Config!$B$7+B33)</f>
         <v>180.666666666667</v>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B37" s="14">
-        <f>IFERROR(B36/(1-Config!$B$8-Config!$B$9),"")</f>
+        <f>IF(NOT(ISNUMBER(B36)),B36,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",B36/(1-Config!$B$8-Config!$B$9)))</f>
         <v>306.214689265537</v>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="B38" s="27">
-        <f>IFERROR(B36/(1-Config!$B$8-Config!$B$10),"")</f>
+        <f>IF(NOT(ISNUMBER(B36)),B36,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",B36/(1-Config!$B$8-Config!$B$10)))</f>
         <v>410.606060606061</v>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="B39" s="16">
-        <f>IF(B34=0,"",(B34*(1-Config!$B$8)-B36)/B34)</f>
+        <f>IF(OR(B34=0,NOT(ISNUMBER(B36))),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
         <v>0.513611111111111</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B40" s="28" t="str">
-        <f>IF(B34=0,"",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))</f>
+        <f>IF(B34=0,"",IF(NOT(ISNUMBER(B36)),"Falta o custo-hora em Config",IF(NOT(ISNUMBER(B37)),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="C40" s="22" t="n"/>
@@ -2381,7 +2381,7 @@
   </mergeCells>
   <conditionalFormatting sqref="K5:K16">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>K5="Abaixo do mínimo"</formula>
+      <formula>OR(K5="Abaixo do mínimo",K5="Falta o custo-hora",K5="Margens inválidas")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>K5="Entre mínimo e alvo"</formula>
@@ -2657,6 +2657,17 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem mínima entre 0 % e a margem alvo, e impostos + margem abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B10),B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1216,48 +1216,48 @@
         <v>130.666666666667</v>
       </c>
       <c r="G5" s="14">
-        <f>IF(A5="","",IF(NOT(ISNUMBER(F5)),F5,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F5/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(F5)),F5,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F5/(1-Config!$B$8-Config!$B$9))))</f>
         <v>221.468926553672</v>
       </c>
       <c r="H5" s="13">
-        <f>IF(A5="","",IF(NOT(ISNUMBER(F5)),F5,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F5/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(F5)),F5,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F5/(1-Config!$B$8-Config!$B$10))))</f>
         <v>296.969696969697</v>
       </c>
       <c r="I5" s="15" t="n">
         <v>380</v>
       </c>
       <c r="J5" s="16">
-        <f>IF(OR(A5="",I5="",I5=0,NOT(ISNUMBER(F5))),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
+        <f>IF(OR(A5="",I5="",I5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
         <v>0.546140350877193</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IF(OR(A5="",I5=""),"",IF(NOT(ISNUMBER(F5)),"Falta o custo-hora",IF(NOT(ISNUMBER(G5)),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A5="",I5=""),"",IF(NOT(ISNUMBER(F5)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L5" s="15" t="n">
         <v>120</v>
       </c>
       <c r="M5" s="16">
-        <f>IF(OR(A5="",L5="",L5=0,NOT(ISNUMBER(F5))),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
+        <f>IF(OR(A5="",L5="",L5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>100</v>
       </c>
       <c r="O5" s="16">
-        <f>IF(OR(A5="",N5="",N5=0,NOT(ISNUMBER(F5))),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
+        <f>IF(OR(A5="",N5="",N5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
         <v>-0.416666666666667</v>
       </c>
       <c r="P5" s="15" t="n">
         <v>90</v>
       </c>
       <c r="Q5" s="16">
-        <f>IF(OR(A5="",P5="",P5=0,NOT(ISNUMBER(F5))),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
+        <f>IF(OR(A5="",P5="",P5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
         <v>-0.561851851851852</v>
       </c>
       <c r="R5" s="15" t="n"/>
       <c r="S5" s="16">
-        <f>IF(OR(A5="",R5="",R5=0,NOT(ISNUMBER(F5))),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
+        <f>IF(OR(A5="",R5="",R5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
         <v/>
       </c>
       <c r="T5" s="18">
@@ -1303,48 +1303,48 @@
         <v>68.6666666666667</v>
       </c>
       <c r="G6" s="14">
-        <f>IF(A6="","",IF(NOT(ISNUMBER(F6)),F6,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F6/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(F6)),F6,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F6/(1-Config!$B$8-Config!$B$9))))</f>
         <v>116.38418079096</v>
       </c>
       <c r="H6" s="13">
-        <f>IF(A6="","",IF(NOT(ISNUMBER(F6)),F6,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F6/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(F6)),F6,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F6/(1-Config!$B$8-Config!$B$10))))</f>
         <v>156.060606060606</v>
       </c>
       <c r="I6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="16">
-        <f>IF(OR(A6="",I6="",I6=0,NOT(ISNUMBER(F6))),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
+        <f>IF(OR(A6="",I6="",I6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
         <v/>
       </c>
       <c r="K6" s="17" t="str">
-        <f>IF(OR(A6="",I6=""),"",IF(NOT(ISNUMBER(F6)),"Falta o custo-hora",IF(NOT(ISNUMBER(G6)),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A6="",I6=""),"",IF(NOT(ISNUMBER(F6)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="L6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f>IF(OR(A6="",L6="",L6=0,NOT(ISNUMBER(F6))),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
+        <f>IF(OR(A6="",L6="",L6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
         <v/>
       </c>
       <c r="N6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="16">
-        <f>IF(OR(A6="",N6="",N6=0,NOT(ISNUMBER(F6))),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
+        <f>IF(OR(A6="",N6="",N6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
         <v/>
       </c>
       <c r="P6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="16">
-        <f>IF(OR(A6="",P6="",P6=0,NOT(ISNUMBER(F6))),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
+        <f>IF(OR(A6="",P6="",P6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
         <v/>
       </c>
       <c r="R6" s="15" t="n"/>
       <c r="S6" s="16">
-        <f>IF(OR(A6="",R6="",R6=0,NOT(ISNUMBER(F6))),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
+        <f>IF(OR(A6="",R6="",R6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
         <v/>
       </c>
       <c r="T6" s="18">
@@ -1390,48 +1390,48 @@
         <v>74.6666666666667</v>
       </c>
       <c r="G7" s="14">
-        <f>IF(A7="","",IF(NOT(ISNUMBER(F7)),F7,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F7/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(F7)),F7,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F7/(1-Config!$B$8-Config!$B$9))))</f>
         <v>126.553672316384</v>
       </c>
       <c r="H7" s="13">
-        <f>IF(A7="","",IF(NOT(ISNUMBER(F7)),F7,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F7/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(F7)),F7,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F7/(1-Config!$B$8-Config!$B$10))))</f>
         <v>169.69696969697</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>130</v>
       </c>
       <c r="J7" s="16">
-        <f>IF(OR(A7="",I7="",I7=0,NOT(ISNUMBER(F7))),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
+        <f>IF(OR(A7="",I7="",I7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
         <v>0.315641025641026</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IF(OR(A7="",I7=""),"",IF(NOT(ISNUMBER(F7)),"Falta o custo-hora",IF(NOT(ISNUMBER(G7)),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A7="",I7=""),"",IF(NOT(ISNUMBER(F7)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="L7" s="15" t="n">
         <v>40</v>
       </c>
       <c r="M7" s="16">
-        <f>IF(OR(A7="",L7="",L7=0,NOT(ISNUMBER(F7))),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
+        <f>IF(OR(A7="",L7="",L7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
         <v>-0.976666666666666</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>35</v>
       </c>
       <c r="O7" s="16">
-        <f>IF(OR(A7="",N7="",N7=0,NOT(ISNUMBER(F7))),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
+        <f>IF(OR(A7="",N7="",N7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
         <v>-1.24333333333333</v>
       </c>
       <c r="P7" s="15" t="n">
         <v>32</v>
       </c>
       <c r="Q7" s="16">
-        <f>IF(OR(A7="",P7="",P7=0,NOT(ISNUMBER(F7))),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
+        <f>IF(OR(A7="",P7="",P7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
         <v>-1.44333333333333</v>
       </c>
       <c r="R7" s="15" t="n"/>
       <c r="S7" s="16">
-        <f>IF(OR(A7="",R7="",R7=0,NOT(ISNUMBER(F7))),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
+        <f>IF(OR(A7="",R7="",R7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
         <v/>
       </c>
       <c r="T7" s="18">
@@ -1477,48 +1477,48 @@
         <v>81.6666666666667</v>
       </c>
       <c r="G8" s="14">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(F8)),F8,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F8/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(F8)),F8,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F8/(1-Config!$B$8-Config!$B$9))))</f>
         <v>138.418079096045</v>
       </c>
       <c r="H8" s="13">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(F8)),F8,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F8/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(F8)),F8,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F8/(1-Config!$B$8-Config!$B$10))))</f>
         <v>185.606060606061</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>300</v>
       </c>
       <c r="J8" s="16">
-        <f>IF(OR(A8="",I8="",I8=0,NOT(ISNUMBER(F8))),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
+        <f>IF(OR(A8="",I8="",I8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
         <v>0.617777777777778</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IF(OR(A8="",I8=""),"",IF(NOT(ISNUMBER(F8)),"Falta o custo-hora",IF(NOT(ISNUMBER(G8)),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A8="",I8=""),"",IF(NOT(ISNUMBER(F8)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L8" s="15" t="n">
         <v>95</v>
       </c>
       <c r="M8" s="16">
-        <f>IF(OR(A8="",L8="",L8=0,NOT(ISNUMBER(F8))),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
+        <f>IF(OR(A8="",L8="",L8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
         <v>0.0303508771929825</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>85</v>
       </c>
       <c r="O8" s="16">
-        <f>IF(OR(A8="",N8="",N8=0,NOT(ISNUMBER(F8))),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
+        <f>IF(OR(A8="",N8="",N8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
         <v>-0.07078431372549</v>
       </c>
       <c r="P8" s="15" t="n">
         <v>75</v>
       </c>
       <c r="Q8" s="16">
-        <f>IF(OR(A8="",P8="",P8=0,NOT(ISNUMBER(F8))),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
+        <f>IF(OR(A8="",P8="",P8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="R8" s="15" t="n"/>
       <c r="S8" s="16">
-        <f>IF(OR(A8="",R8="",R8=0,NOT(ISNUMBER(F8))),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
+        <f>IF(OR(A8="",R8="",R8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
         <v/>
       </c>
       <c r="T8" s="18">
@@ -1564,48 +1564,48 @@
         <v>84.6666666666667</v>
       </c>
       <c r="G9" s="14">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(F9)),F9,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F9/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(F9)),F9,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F9/(1-Config!$B$8-Config!$B$9))))</f>
         <v>143.502824858757</v>
       </c>
       <c r="H9" s="13">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(F9)),F9,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F9/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(F9)),F9,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F9/(1-Config!$B$8-Config!$B$10))))</f>
         <v>192.424242424242</v>
       </c>
       <c r="I9" s="15" t="n">
         <v>350</v>
       </c>
       <c r="J9" s="16">
-        <f>IF(OR(A9="",I9="",I9=0,NOT(ISNUMBER(F9))),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
+        <f>IF(OR(A9="",I9="",I9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
         <v>0.648095238095238</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IF(OR(A9="",I9=""),"",IF(NOT(ISNUMBER(F9)),"Falta o custo-hora",IF(NOT(ISNUMBER(G9)),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A9="",I9=""),"",IF(NOT(ISNUMBER(F9)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L9" s="15" t="n">
         <v>105</v>
       </c>
       <c r="M9" s="16">
-        <f>IF(OR(A9="",L9="",L9=0,NOT(ISNUMBER(F9))),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
+        <f>IF(OR(A9="",L9="",L9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
         <v>0.0836507936507938</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>95</v>
       </c>
       <c r="O9" s="16">
-        <f>IF(OR(A9="",N9="",N9=0,NOT(ISNUMBER(F9))),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
+        <f>IF(OR(A9="",N9="",N9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
         <v>-0.00122807017543853</v>
       </c>
       <c r="P9" s="15" t="n">
         <v>85</v>
       </c>
       <c r="Q9" s="16">
-        <f>IF(OR(A9="",P9="",P9=0,NOT(ISNUMBER(F9))),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
+        <f>IF(OR(A9="",P9="",P9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
         <v>-0.106078431372549</v>
       </c>
       <c r="R9" s="15" t="n"/>
       <c r="S9" s="16">
-        <f>IF(OR(A9="",R9="",R9=0,NOT(ISNUMBER(F9))),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
+        <f>IF(OR(A9="",R9="",R9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
         <v/>
       </c>
       <c r="T9" s="18">
@@ -1651,48 +1651,48 @@
         <v>158.333333333333</v>
       </c>
       <c r="G10" s="14">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(F10)),F10,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F10/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(F10)),F10,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F10/(1-Config!$B$8-Config!$B$9))))</f>
         <v>268.361581920904</v>
       </c>
       <c r="H10" s="13">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(F10)),F10,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F10/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(F10)),F10,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F10/(1-Config!$B$8-Config!$B$10))))</f>
         <v>359.848484848485</v>
       </c>
       <c r="I10" s="15" t="n">
         <v>450</v>
       </c>
       <c r="J10" s="16">
-        <f>IF(OR(A10="",I10="",I10=0,NOT(ISNUMBER(F10))),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
+        <f>IF(OR(A10="",I10="",I10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
         <v>0.538148148148148</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IF(OR(A10="",I10=""),"",IF(NOT(ISNUMBER(F10)),"Falta o custo-hora",IF(NOT(ISNUMBER(G10)),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A10="",I10=""),"",IF(NOT(ISNUMBER(F10)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>140</v>
       </c>
       <c r="M10" s="16">
-        <f>IF(OR(A10="",L10="",L10=0,NOT(ISNUMBER(F10))),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
+        <f>IF(OR(A10="",L10="",L10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
         <v>-0.240952380952381</v>
       </c>
       <c r="N10" s="15" t="n">
         <v>125</v>
       </c>
       <c r="O10" s="16">
-        <f>IF(OR(A10="",N10="",N10=0,NOT(ISNUMBER(F10))),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
+        <f>IF(OR(A10="",N10="",N10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
         <v>-0.376666666666667</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>110</v>
       </c>
       <c r="Q10" s="16">
-        <f>IF(OR(A10="",P10="",P10=0,NOT(ISNUMBER(F10))),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
+        <f>IF(OR(A10="",P10="",P10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
         <v>-0.549393939393939</v>
       </c>
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="16">
-        <f>IF(OR(A10="",R10="",R10=0,NOT(ISNUMBER(F10))),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
+        <f>IF(OR(A10="",R10="",R10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
         <v/>
       </c>
       <c r="T10" s="18">
@@ -1738,44 +1738,44 @@
         <v>164</v>
       </c>
       <c r="G11" s="14">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(F11)),F11,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F11/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(F11)),F11,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F11/(1-Config!$B$8-Config!$B$9))))</f>
         <v>277.966101694915</v>
       </c>
       <c r="H11" s="13">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(F11)),F11,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F11/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(F11)),F11,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F11/(1-Config!$B$8-Config!$B$10))))</f>
         <v>372.727272727273</v>
       </c>
       <c r="I11" s="15" t="n">
         <v>400</v>
       </c>
       <c r="J11" s="16">
-        <f>IF(OR(A11="",I11="",I11=0,NOT(ISNUMBER(F11))),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
+        <f>IF(OR(A11="",I11="",I11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
         <v>0.48</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IF(OR(A11="",I11=""),"",IF(NOT(ISNUMBER(F11)),"Falta o custo-hora",IF(NOT(ISNUMBER(G11)),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A11="",I11=""),"",IF(NOT(ISNUMBER(F11)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L11" s="15" t="n">
         <v>130</v>
       </c>
       <c r="M11" s="16">
-        <f>IF(OR(A11="",L11="",L11=0,NOT(ISNUMBER(F11))),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
+        <f>IF(OR(A11="",L11="",L11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
         <v>-0.371538461538462</v>
       </c>
       <c r="N11" s="15" t="n"/>
       <c r="O11" s="16">
-        <f>IF(OR(A11="",N11="",N11=0,NOT(ISNUMBER(F11))),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
+        <f>IF(OR(A11="",N11="",N11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
         <v/>
       </c>
       <c r="P11" s="15" t="n"/>
       <c r="Q11" s="16">
-        <f>IF(OR(A11="",P11="",P11=0,NOT(ISNUMBER(F11))),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
+        <f>IF(OR(A11="",P11="",P11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
         <v/>
       </c>
       <c r="R11" s="15" t="n"/>
       <c r="S11" s="16">
-        <f>IF(OR(A11="",R11="",R11=0,NOT(ISNUMBER(F11))),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
+        <f>IF(OR(A11="",R11="",R11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
         <v/>
       </c>
       <c r="T11" s="18">
@@ -1809,40 +1809,40 @@
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(F12)),F12,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F12/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(F12)),F12,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F12/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(F12)),F12,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F12/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(F12)),F12,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F12/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="16">
-        <f>IF(OR(A12="",I12="",I12=0,NOT(ISNUMBER(F12))),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
+        <f>IF(OR(A12="",I12="",I12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF(OR(A12="",I12=""),"",IF(NOT(ISNUMBER(F12)),"Falta o custo-hora",IF(NOT(ISNUMBER(G12)),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A12="",I12=""),"",IF(NOT(ISNUMBER(F12)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="16">
-        <f>IF(OR(A12="",L12="",L12=0,NOT(ISNUMBER(F12))),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
+        <f>IF(OR(A12="",L12="",L12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
         <v/>
       </c>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="16">
-        <f>IF(OR(A12="",N12="",N12=0,NOT(ISNUMBER(F12))),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
+        <f>IF(OR(A12="",N12="",N12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
         <v/>
       </c>
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="16">
-        <f>IF(OR(A12="",P12="",P12=0,NOT(ISNUMBER(F12))),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
+        <f>IF(OR(A12="",P12="",P12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
         <v/>
       </c>
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="16">
-        <f>IF(OR(A12="",R12="",R12=0,NOT(ISNUMBER(F12))),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
+        <f>IF(OR(A12="",R12="",R12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
         <v/>
       </c>
       <c r="T12" s="18">
@@ -1876,40 +1876,40 @@
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(F13)),F13,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F13/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(F13)),F13,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F13/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(F13)),F13,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F13/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(F13)),F13,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F13/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I13" s="15" t="n"/>
       <c r="J13" s="16">
-        <f>IF(OR(A13="",I13="",I13=0,NOT(ISNUMBER(F13))),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
+        <f>IF(OR(A13="",I13="",I13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF(OR(A13="",I13=""),"",IF(NOT(ISNUMBER(F13)),"Falta o custo-hora",IF(NOT(ISNUMBER(G13)),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A13="",I13=""),"",IF(NOT(ISNUMBER(F13)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="16">
-        <f>IF(OR(A13="",L13="",L13=0,NOT(ISNUMBER(F13))),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
+        <f>IF(OR(A13="",L13="",L13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
         <v/>
       </c>
       <c r="N13" s="15" t="n"/>
       <c r="O13" s="16">
-        <f>IF(OR(A13="",N13="",N13=0,NOT(ISNUMBER(F13))),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
+        <f>IF(OR(A13="",N13="",N13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
         <v/>
       </c>
       <c r="P13" s="15" t="n"/>
       <c r="Q13" s="16">
-        <f>IF(OR(A13="",P13="",P13=0,NOT(ISNUMBER(F13))),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
+        <f>IF(OR(A13="",P13="",P13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
         <v/>
       </c>
       <c r="R13" s="15" t="n"/>
       <c r="S13" s="16">
-        <f>IF(OR(A13="",R13="",R13=0,NOT(ISNUMBER(F13))),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
+        <f>IF(OR(A13="",R13="",R13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
         <v/>
       </c>
       <c r="T13" s="18">
@@ -1943,40 +1943,40 @@
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(F14)),F14,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F14/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(F14)),F14,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F14/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H14" s="13">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(F14)),F14,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F14/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(F14)),F14,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F14/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I14" s="15" t="n"/>
       <c r="J14" s="16">
-        <f>IF(OR(A14="",I14="",I14=0,NOT(ISNUMBER(F14))),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
+        <f>IF(OR(A14="",I14="",I14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF(OR(A14="",I14=""),"",IF(NOT(ISNUMBER(F14)),"Falta o custo-hora",IF(NOT(ISNUMBER(G14)),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A14="",I14=""),"",IF(NOT(ISNUMBER(F14)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="16">
-        <f>IF(OR(A14="",L14="",L14=0,NOT(ISNUMBER(F14))),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
+        <f>IF(OR(A14="",L14="",L14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
         <v/>
       </c>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="16">
-        <f>IF(OR(A14="",N14="",N14=0,NOT(ISNUMBER(F14))),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
+        <f>IF(OR(A14="",N14="",N14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
         <v/>
       </c>
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="16">
-        <f>IF(OR(A14="",P14="",P14=0,NOT(ISNUMBER(F14))),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
+        <f>IF(OR(A14="",P14="",P14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
         <v/>
       </c>
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="16">
-        <f>IF(OR(A14="",R14="",R14=0,NOT(ISNUMBER(F14))),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
+        <f>IF(OR(A14="",R14="",R14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
         <v/>
       </c>
       <c r="T14" s="18">
@@ -2010,40 +2010,40 @@
         <v/>
       </c>
       <c r="G15" s="14">
-        <f>IF(A15="","",IF(NOT(ISNUMBER(F15)),F15,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F15/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(F15)),F15,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F15/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>IF(A15="","",IF(NOT(ISNUMBER(F15)),F15,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F15/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(F15)),F15,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F15/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="16">
-        <f>IF(OR(A15="",I15="",I15=0,NOT(ISNUMBER(F15))),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
+        <f>IF(OR(A15="",I15="",I15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF(OR(A15="",I15=""),"",IF(NOT(ISNUMBER(F15)),"Falta o custo-hora",IF(NOT(ISNUMBER(G15)),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A15="",I15=""),"",IF(NOT(ISNUMBER(F15)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="16">
-        <f>IF(OR(A15="",L15="",L15=0,NOT(ISNUMBER(F15))),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
+        <f>IF(OR(A15="",L15="",L15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
         <v/>
       </c>
       <c r="N15" s="15" t="n"/>
       <c r="O15" s="16">
-        <f>IF(OR(A15="",N15="",N15=0,NOT(ISNUMBER(F15))),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
+        <f>IF(OR(A15="",N15="",N15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
         <v/>
       </c>
       <c r="P15" s="15" t="n"/>
       <c r="Q15" s="16">
-        <f>IF(OR(A15="",P15="",P15=0,NOT(ISNUMBER(F15))),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
+        <f>IF(OR(A15="",P15="",P15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
         <v/>
       </c>
       <c r="R15" s="15" t="n"/>
       <c r="S15" s="16">
-        <f>IF(OR(A15="",R15="",R15=0,NOT(ISNUMBER(F15))),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
+        <f>IF(OR(A15="",R15="",R15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
         <v/>
       </c>
       <c r="T15" s="18">
@@ -2077,40 +2077,40 @@
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>IF(A16="","",IF(NOT(ISNUMBER(F16)),F16,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",F16/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(F16)),F16,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F16/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="H16" s="13">
-        <f>IF(A16="","",IF(NOT(ISNUMBER(F16)),F16,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",F16/(1-Config!$B$8-Config!$B$10))))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(F16)),F16,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",F16/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="16">
-        <f>IF(OR(A16="",I16="",I16=0,NOT(ISNUMBER(F16))),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
+        <f>IF(OR(A16="",I16="",I16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF(OR(A16="",I16=""),"",IF(NOT(ISNUMBER(F16)),"Falta o custo-hora",IF(NOT(ISNUMBER(G16)),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A16="",I16=""),"",IF(NOT(ISNUMBER(F16)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="16">
-        <f>IF(OR(A16="",L16="",L16=0,NOT(ISNUMBER(F16))),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
+        <f>IF(OR(A16="",L16="",L16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
         <v/>
       </c>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="16">
-        <f>IF(OR(A16="",N16="",N16=0,NOT(ISNUMBER(F16))),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
+        <f>IF(OR(A16="",N16="",N16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
         <v/>
       </c>
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="16">
-        <f>IF(OR(A16="",P16="",P16=0,NOT(ISNUMBER(F16))),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
+        <f>IF(OR(A16="",P16="",P16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
         <v/>
       </c>
       <c r="R16" s="15" t="n"/>
       <c r="S16" s="16">
-        <f>IF(OR(A16="",R16="",R16=0,NOT(ISNUMBER(F16))),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
+        <f>IF(OR(A16="",R16="",R16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
         <v/>
       </c>
       <c r="T16" s="18">
@@ -2163,7 +2163,7 @@
       <c r="C22" s="22" t="n"/>
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="14">
-        <f>Config!$B$7</f>
+        <f>IF(ISNUMBER(Config!$B$7),Config!$B$7,"falta o custo-hora em Config")</f>
         <v>200</v>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="14">
-        <f>IFERROR(Config!$B$7/(1-Config!$B$8-Config!$B$9),"")</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",Config!$B$7/(1-Config!$B$8-Config!$B$9)))</f>
         <v>338.983050847458</v>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="24" t="str">
-        <f>COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16)</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16)))</f>
         <v>0 de 7</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="25">
-        <f>COUNTIF($T$5:$W$16,"&lt;0")</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",COUNTIF($T$5:$W$16,"&lt;0")))</f>
         <v>14</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="14">
-        <f>-MIN($T$5:$W$16)</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",-MIN($T$5:$W$16)))</f>
         <v>60.4333333333333</v>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B37" s="14">
-        <f>IF(NOT(ISNUMBER(B36)),B36,IF((1-Config!$B$8-Config!$B$9)&lt;=0,"margens inválidas (Config)",B36/(1-Config!$B$8-Config!$B$9)))</f>
+        <f>IF(NOT(ISNUMBER(B36)),B36,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",B36/(1-Config!$B$8-Config!$B$9)))</f>
         <v>306.214689265537</v>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="B38" s="27">
-        <f>IF(NOT(ISNUMBER(B36)),B36,IF((1-Config!$B$8-Config!$B$10)&lt;=0,"margens inválidas (Config)",B36/(1-Config!$B$8-Config!$B$10)))</f>
+        <f>IF(NOT(ISNUMBER(B36)),B36,IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",B36/(1-Config!$B$8-Config!$B$10)))</f>
         <v>410.606060606061</v>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="B39" s="16">
-        <f>IF(OR(B34=0,NOT(ISNUMBER(B36))),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
+        <f>IF(OR(B34=0,NOT(ISNUMBER(B36)),(Config!$B$13&lt;&gt;"Sim")),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
         <v>0.513611111111111</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B40" s="28" t="str">
-        <f>IF(B34=0,"",IF(NOT(ISNUMBER(B36)),"Falta o custo-hora em Config",IF(NOT(ISNUMBER(B37)),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))</f>
+        <f>IF(B34=0,"",IF(NOT(ISNUMBER(B36)),"Falta o custo-hora em Config",IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="C40" s="22" t="n"/>
@@ -2610,6 +2610,22 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Impostos e margens conferem? (calculado)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="str">
+        <f>IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10)),IF(AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1),"Sim","Não"),"Não")</f>
+        <v>Sim</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>"Não" suspende preços, margens, situação e resumo: impostos e margens de 0 % a 99 %, mínima ≤ alvo e impostos + margem alvo abaixo de 100 %.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -2675,13 +2675,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem mínima entre 0 % e a margem alvo, e impostos + margem abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B9),AND(B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B10),B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B10),AND(B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1208,11 +1208,11 @@
         <v>4</v>
       </c>
       <c r="E5" s="12">
-        <f>IF(A5="","",B5+IF(C5="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A5="","",IF(NOT(IF(ISNUMBER(B5),AND(B5&gt;=0),FALSE)),"faltam os minutos",IF(AND(C5&lt;&gt;"Sim",C5&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C5="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B5+IF(C5="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>38</v>
       </c>
       <c r="F5" s="13">
-        <f>IF(A5="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E5/60*Config!$B$7+D5))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(E5)),E5,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D5),AND(D5&gt;=0),FALSE)),"falta o material",E5/60*Config!$B$7+D5))))</f>
         <v>130.666666666667</v>
       </c>
       <c r="G5" s="14">
@@ -1227,37 +1227,37 @@
         <v>380</v>
       </c>
       <c r="J5" s="16">
-        <f>IF(OR(A5="",I5="",I5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
+        <f>IF(OR(A5="",I5="",NOT(ISNUMBER(I5)),N(I5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
         <v>0.546140350877193</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IF(OR(A5="",I5=""),"",IF(NOT(ISNUMBER(F5)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A5="",I5=""),"",IF(NOT(ISNUMBER(I5)),"Preço inválido",IF(NOT(ISNUMBER(F5)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L5" s="15" t="n">
         <v>120</v>
       </c>
       <c r="M5" s="16">
-        <f>IF(OR(A5="",L5="",L5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
+        <f>IF(OR(A5="",L5="",NOT(ISNUMBER(L5)),N(L5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>100</v>
       </c>
       <c r="O5" s="16">
-        <f>IF(OR(A5="",N5="",N5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
+        <f>IF(OR(A5="",N5="",NOT(ISNUMBER(N5)),N(N5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
         <v>-0.416666666666667</v>
       </c>
       <c r="P5" s="15" t="n">
         <v>90</v>
       </c>
       <c r="Q5" s="16">
-        <f>IF(OR(A5="",P5="",P5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
+        <f>IF(OR(A5="",P5="",NOT(ISNUMBER(P5)),N(P5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
         <v>-0.561851851851852</v>
       </c>
       <c r="R5" s="15" t="n"/>
       <c r="S5" s="16">
-        <f>IF(OR(A5="",R5="",R5=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
+        <f>IF(OR(A5="",R5="",NOT(ISNUMBER(R5)),N(R5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
         <v/>
       </c>
       <c r="T5" s="18">
@@ -1295,11 +1295,11 @@
         <v>2</v>
       </c>
       <c r="E6" s="12">
-        <f>IF(A6="","",B6+IF(C6="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A6="","",IF(NOT(IF(ISNUMBER(B6),AND(B6&gt;=0),FALSE)),"faltam os minutos",IF(AND(C6&lt;&gt;"Sim",C6&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C6="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B6+IF(C6="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="F6" s="13">
-        <f>IF(A6="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E6/60*Config!$B$7+D6))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(E6)),E6,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D6),AND(D6&gt;=0),FALSE)),"falta o material",E6/60*Config!$B$7+D6))))</f>
         <v>68.6666666666667</v>
       </c>
       <c r="G6" s="14">
@@ -1314,37 +1314,37 @@
         <v>0</v>
       </c>
       <c r="J6" s="16">
-        <f>IF(OR(A6="",I6="",I6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
+        <f>IF(OR(A6="",I6="",NOT(ISNUMBER(I6)),N(I6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
         <v/>
       </c>
       <c r="K6" s="17" t="str">
-        <f>IF(OR(A6="",I6=""),"",IF(NOT(ISNUMBER(F6)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A6="",I6=""),"",IF(NOT(ISNUMBER(I6)),"Preço inválido",IF(NOT(ISNUMBER(F6)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="L6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f>IF(OR(A6="",L6="",L6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
+        <f>IF(OR(A6="",L6="",NOT(ISNUMBER(L6)),N(L6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
         <v/>
       </c>
       <c r="N6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="16">
-        <f>IF(OR(A6="",N6="",N6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
+        <f>IF(OR(A6="",N6="",NOT(ISNUMBER(N6)),N(N6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
         <v/>
       </c>
       <c r="P6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="16">
-        <f>IF(OR(A6="",P6="",P6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
+        <f>IF(OR(A6="",P6="",NOT(ISNUMBER(P6)),N(P6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
         <v/>
       </c>
       <c r="R6" s="15" t="n"/>
       <c r="S6" s="16">
-        <f>IF(OR(A6="",R6="",R6=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
+        <f>IF(OR(A6="",R6="",NOT(ISNUMBER(R6)),N(R6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
         <v/>
       </c>
       <c r="T6" s="18">
@@ -1382,11 +1382,11 @@
         <v>8</v>
       </c>
       <c r="E7" s="12">
-        <f>IF(A7="","",B7+IF(C7="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A7="","",IF(NOT(IF(ISNUMBER(B7),AND(B7&gt;=0),FALSE)),"faltam os minutos",IF(AND(C7&lt;&gt;"Sim",C7&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C7="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B7+IF(C7="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="F7" s="13">
-        <f>IF(A7="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E7/60*Config!$B$7+D7))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(E7)),E7,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D7),AND(D7&gt;=0),FALSE)),"falta o material",E7/60*Config!$B$7+D7))))</f>
         <v>74.6666666666667</v>
       </c>
       <c r="G7" s="14">
@@ -1401,37 +1401,37 @@
         <v>130</v>
       </c>
       <c r="J7" s="16">
-        <f>IF(OR(A7="",I7="",I7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
+        <f>IF(OR(A7="",I7="",NOT(ISNUMBER(I7)),N(I7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
         <v>0.315641025641026</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IF(OR(A7="",I7=""),"",IF(NOT(ISNUMBER(F7)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A7="",I7=""),"",IF(NOT(ISNUMBER(I7)),"Preço inválido",IF(NOT(ISNUMBER(F7)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="L7" s="15" t="n">
         <v>40</v>
       </c>
       <c r="M7" s="16">
-        <f>IF(OR(A7="",L7="",L7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
+        <f>IF(OR(A7="",L7="",NOT(ISNUMBER(L7)),N(L7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
         <v>-0.976666666666666</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>35</v>
       </c>
       <c r="O7" s="16">
-        <f>IF(OR(A7="",N7="",N7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
+        <f>IF(OR(A7="",N7="",NOT(ISNUMBER(N7)),N(N7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
         <v>-1.24333333333333</v>
       </c>
       <c r="P7" s="15" t="n">
         <v>32</v>
       </c>
       <c r="Q7" s="16">
-        <f>IF(OR(A7="",P7="",P7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
+        <f>IF(OR(A7="",P7="",NOT(ISNUMBER(P7)),N(P7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
         <v>-1.44333333333333</v>
       </c>
       <c r="R7" s="15" t="n"/>
       <c r="S7" s="16">
-        <f>IF(OR(A7="",R7="",R7=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
+        <f>IF(OR(A7="",R7="",NOT(ISNUMBER(R7)),N(R7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
         <v/>
       </c>
       <c r="T7" s="18">
@@ -1469,11 +1469,11 @@
         <v>15</v>
       </c>
       <c r="E8" s="12">
-        <f>IF(A8="","",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A8="","",IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="F8" s="13">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E8/60*Config!$B$7+D8))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(E8)),E8,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D8),AND(D8&gt;=0),FALSE)),"falta o material",E8/60*Config!$B$7+D8))))</f>
         <v>81.6666666666667</v>
       </c>
       <c r="G8" s="14">
@@ -1488,37 +1488,37 @@
         <v>300</v>
       </c>
       <c r="J8" s="16">
-        <f>IF(OR(A8="",I8="",I8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
+        <f>IF(OR(A8="",I8="",NOT(ISNUMBER(I8)),N(I8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
         <v>0.617777777777778</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IF(OR(A8="",I8=""),"",IF(NOT(ISNUMBER(F8)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A8="",I8=""),"",IF(NOT(ISNUMBER(I8)),"Preço inválido",IF(NOT(ISNUMBER(F8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L8" s="15" t="n">
         <v>95</v>
       </c>
       <c r="M8" s="16">
-        <f>IF(OR(A8="",L8="",L8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
+        <f>IF(OR(A8="",L8="",NOT(ISNUMBER(L8)),N(L8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
         <v>0.0303508771929825</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>85</v>
       </c>
       <c r="O8" s="16">
-        <f>IF(OR(A8="",N8="",N8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
+        <f>IF(OR(A8="",N8="",NOT(ISNUMBER(N8)),N(N8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
         <v>-0.07078431372549</v>
       </c>
       <c r="P8" s="15" t="n">
         <v>75</v>
       </c>
       <c r="Q8" s="16">
-        <f>IF(OR(A8="",P8="",P8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
+        <f>IF(OR(A8="",P8="",NOT(ISNUMBER(P8)),N(P8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="R8" s="15" t="n"/>
       <c r="S8" s="16">
-        <f>IF(OR(A8="",R8="",R8=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
+        <f>IF(OR(A8="",R8="",NOT(ISNUMBER(R8)),N(R8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
         <v/>
       </c>
       <c r="T8" s="18">
@@ -1556,11 +1556,11 @@
         <v>18</v>
       </c>
       <c r="E9" s="12">
-        <f>IF(A9="","",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A9="","",IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="F9" s="13">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E9/60*Config!$B$7+D9))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(E9)),E9,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D9),AND(D9&gt;=0),FALSE)),"falta o material",E9/60*Config!$B$7+D9))))</f>
         <v>84.6666666666667</v>
       </c>
       <c r="G9" s="14">
@@ -1575,37 +1575,37 @@
         <v>350</v>
       </c>
       <c r="J9" s="16">
-        <f>IF(OR(A9="",I9="",I9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
+        <f>IF(OR(A9="",I9="",NOT(ISNUMBER(I9)),N(I9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
         <v>0.648095238095238</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IF(OR(A9="",I9=""),"",IF(NOT(ISNUMBER(F9)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A9="",I9=""),"",IF(NOT(ISNUMBER(I9)),"Preço inválido",IF(NOT(ISNUMBER(F9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L9" s="15" t="n">
         <v>105</v>
       </c>
       <c r="M9" s="16">
-        <f>IF(OR(A9="",L9="",L9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
+        <f>IF(OR(A9="",L9="",NOT(ISNUMBER(L9)),N(L9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
         <v>0.0836507936507938</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>95</v>
       </c>
       <c r="O9" s="16">
-        <f>IF(OR(A9="",N9="",N9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
+        <f>IF(OR(A9="",N9="",NOT(ISNUMBER(N9)),N(N9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
         <v>-0.00122807017543853</v>
       </c>
       <c r="P9" s="15" t="n">
         <v>85</v>
       </c>
       <c r="Q9" s="16">
-        <f>IF(OR(A9="",P9="",P9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
+        <f>IF(OR(A9="",P9="",NOT(ISNUMBER(P9)),N(P9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
         <v>-0.106078431372549</v>
       </c>
       <c r="R9" s="15" t="n"/>
       <c r="S9" s="16">
-        <f>IF(OR(A9="",R9="",R9=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
+        <f>IF(OR(A9="",R9="",NOT(ISNUMBER(R9)),N(R9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
         <v/>
       </c>
       <c r="T9" s="18">
@@ -1643,11 +1643,11 @@
         <v>25</v>
       </c>
       <c r="E10" s="12">
-        <f>IF(A10="","",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A10="","",IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>40</v>
       </c>
       <c r="F10" s="13">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E10/60*Config!$B$7+D10))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(E10)),E10,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D10),AND(D10&gt;=0),FALSE)),"falta o material",E10/60*Config!$B$7+D10))))</f>
         <v>158.333333333333</v>
       </c>
       <c r="G10" s="14">
@@ -1662,37 +1662,37 @@
         <v>450</v>
       </c>
       <c r="J10" s="16">
-        <f>IF(OR(A10="",I10="",I10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
+        <f>IF(OR(A10="",I10="",NOT(ISNUMBER(I10)),N(I10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
         <v>0.538148148148148</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IF(OR(A10="",I10=""),"",IF(NOT(ISNUMBER(F10)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A10="",I10=""),"",IF(NOT(ISNUMBER(I10)),"Preço inválido",IF(NOT(ISNUMBER(F10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>140</v>
       </c>
       <c r="M10" s="16">
-        <f>IF(OR(A10="",L10="",L10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
+        <f>IF(OR(A10="",L10="",NOT(ISNUMBER(L10)),N(L10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
         <v>-0.240952380952381</v>
       </c>
       <c r="N10" s="15" t="n">
         <v>125</v>
       </c>
       <c r="O10" s="16">
-        <f>IF(OR(A10="",N10="",N10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
+        <f>IF(OR(A10="",N10="",NOT(ISNUMBER(N10)),N(N10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
         <v>-0.376666666666667</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>110</v>
       </c>
       <c r="Q10" s="16">
-        <f>IF(OR(A10="",P10="",P10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
+        <f>IF(OR(A10="",P10="",NOT(ISNUMBER(P10)),N(P10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
         <v>-0.549393939393939</v>
       </c>
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="16">
-        <f>IF(OR(A10="",R10="",R10=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
+        <f>IF(OR(A10="",R10="",NOT(ISNUMBER(R10)),N(R10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
         <v/>
       </c>
       <c r="T10" s="18">
@@ -1730,11 +1730,11 @@
         <v>4</v>
       </c>
       <c r="E11" s="12">
-        <f>IF(A11="","",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A11="","",IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>48</v>
       </c>
       <c r="F11" s="13">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E11/60*Config!$B$7+D11))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(E11)),E11,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D11),AND(D11&gt;=0),FALSE)),"falta o material",E11/60*Config!$B$7+D11))))</f>
         <v>164</v>
       </c>
       <c r="G11" s="14">
@@ -1749,33 +1749,33 @@
         <v>400</v>
       </c>
       <c r="J11" s="16">
-        <f>IF(OR(A11="",I11="",I11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
+        <f>IF(OR(A11="",I11="",NOT(ISNUMBER(I11)),N(I11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
         <v>0.48</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IF(OR(A11="",I11=""),"",IF(NOT(ISNUMBER(F11)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A11="",I11=""),"",IF(NOT(ISNUMBER(I11)),"Preço inválido",IF(NOT(ISNUMBER(F11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L11" s="15" t="n">
         <v>130</v>
       </c>
       <c r="M11" s="16">
-        <f>IF(OR(A11="",L11="",L11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
+        <f>IF(OR(A11="",L11="",NOT(ISNUMBER(L11)),N(L11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
         <v>-0.371538461538462</v>
       </c>
       <c r="N11" s="15" t="n"/>
       <c r="O11" s="16">
-        <f>IF(OR(A11="",N11="",N11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
+        <f>IF(OR(A11="",N11="",NOT(ISNUMBER(N11)),N(N11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
         <v/>
       </c>
       <c r="P11" s="15" t="n"/>
       <c r="Q11" s="16">
-        <f>IF(OR(A11="",P11="",P11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
+        <f>IF(OR(A11="",P11="",NOT(ISNUMBER(P11)),N(P11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
         <v/>
       </c>
       <c r="R11" s="15" t="n"/>
       <c r="S11" s="16">
-        <f>IF(OR(A11="",R11="",R11=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
+        <f>IF(OR(A11="",R11="",NOT(ISNUMBER(R11)),N(R11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
         <v/>
       </c>
       <c r="T11" s="18">
@@ -1801,11 +1801,11 @@
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="12">
-        <f>IF(A12="","",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A12="","",IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E12/60*Config!$B$7+D12))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(E12)),E12,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D12),AND(D12&gt;=0),FALSE)),"falta o material",E12/60*Config!$B$7+D12))))</f>
         <v/>
       </c>
       <c r="G12" s="14">
@@ -1818,31 +1818,31 @@
       </c>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="16">
-        <f>IF(OR(A12="",I12="",I12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
+        <f>IF(OR(A12="",I12="",NOT(ISNUMBER(I12)),N(I12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF(OR(A12="",I12=""),"",IF(NOT(ISNUMBER(F12)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A12="",I12=""),"",IF(NOT(ISNUMBER(I12)),"Preço inválido",IF(NOT(ISNUMBER(F12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="16">
-        <f>IF(OR(A12="",L12="",L12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
+        <f>IF(OR(A12="",L12="",NOT(ISNUMBER(L12)),N(L12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
         <v/>
       </c>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="16">
-        <f>IF(OR(A12="",N12="",N12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
+        <f>IF(OR(A12="",N12="",NOT(ISNUMBER(N12)),N(N12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
         <v/>
       </c>
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="16">
-        <f>IF(OR(A12="",P12="",P12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
+        <f>IF(OR(A12="",P12="",NOT(ISNUMBER(P12)),N(P12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
         <v/>
       </c>
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="16">
-        <f>IF(OR(A12="",R12="",R12=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
+        <f>IF(OR(A12="",R12="",NOT(ISNUMBER(R12)),N(R12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
         <v/>
       </c>
       <c r="T12" s="18">
@@ -1868,11 +1868,11 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="12">
-        <f>IF(A13="","",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A13="","",IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E13/60*Config!$B$7+D13))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(E13)),E13,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D13),AND(D13&gt;=0),FALSE)),"falta o material",E13/60*Config!$B$7+D13))))</f>
         <v/>
       </c>
       <c r="G13" s="14">
@@ -1885,31 +1885,31 @@
       </c>
       <c r="I13" s="15" t="n"/>
       <c r="J13" s="16">
-        <f>IF(OR(A13="",I13="",I13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
+        <f>IF(OR(A13="",I13="",NOT(ISNUMBER(I13)),N(I13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF(OR(A13="",I13=""),"",IF(NOT(ISNUMBER(F13)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A13="",I13=""),"",IF(NOT(ISNUMBER(I13)),"Preço inválido",IF(NOT(ISNUMBER(F13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="16">
-        <f>IF(OR(A13="",L13="",L13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
+        <f>IF(OR(A13="",L13="",NOT(ISNUMBER(L13)),N(L13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
         <v/>
       </c>
       <c r="N13" s="15" t="n"/>
       <c r="O13" s="16">
-        <f>IF(OR(A13="",N13="",N13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
+        <f>IF(OR(A13="",N13="",NOT(ISNUMBER(N13)),N(N13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
         <v/>
       </c>
       <c r="P13" s="15" t="n"/>
       <c r="Q13" s="16">
-        <f>IF(OR(A13="",P13="",P13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
+        <f>IF(OR(A13="",P13="",NOT(ISNUMBER(P13)),N(P13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
         <v/>
       </c>
       <c r="R13" s="15" t="n"/>
       <c r="S13" s="16">
-        <f>IF(OR(A13="",R13="",R13=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
+        <f>IF(OR(A13="",R13="",NOT(ISNUMBER(R13)),N(R13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
         <v/>
       </c>
       <c r="T13" s="18">
@@ -1935,11 +1935,11 @@
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="12">
-        <f>IF(A14="","",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A14="","",IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="F14" s="13">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E14/60*Config!$B$7+D14))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(E14)),E14,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D14),AND(D14&gt;=0),FALSE)),"falta o material",E14/60*Config!$B$7+D14))))</f>
         <v/>
       </c>
       <c r="G14" s="14">
@@ -1952,31 +1952,31 @@
       </c>
       <c r="I14" s="15" t="n"/>
       <c r="J14" s="16">
-        <f>IF(OR(A14="",I14="",I14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
+        <f>IF(OR(A14="",I14="",NOT(ISNUMBER(I14)),N(I14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF(OR(A14="",I14=""),"",IF(NOT(ISNUMBER(F14)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A14="",I14=""),"",IF(NOT(ISNUMBER(I14)),"Preço inválido",IF(NOT(ISNUMBER(F14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="16">
-        <f>IF(OR(A14="",L14="",L14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
+        <f>IF(OR(A14="",L14="",NOT(ISNUMBER(L14)),N(L14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
         <v/>
       </c>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="16">
-        <f>IF(OR(A14="",N14="",N14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
+        <f>IF(OR(A14="",N14="",NOT(ISNUMBER(N14)),N(N14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
         <v/>
       </c>
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="16">
-        <f>IF(OR(A14="",P14="",P14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
+        <f>IF(OR(A14="",P14="",NOT(ISNUMBER(P14)),N(P14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
         <v/>
       </c>
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="16">
-        <f>IF(OR(A14="",R14="",R14=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
+        <f>IF(OR(A14="",R14="",NOT(ISNUMBER(R14)),N(R14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
         <v/>
       </c>
       <c r="T14" s="18">
@@ -2002,11 +2002,11 @@
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="12">
-        <f>IF(A15="","",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A15="","",IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>IF(A15="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E15/60*Config!$B$7+D15))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(E15)),E15,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D15),AND(D15&gt;=0),FALSE)),"falta o material",E15/60*Config!$B$7+D15))))</f>
         <v/>
       </c>
       <c r="G15" s="14">
@@ -2019,31 +2019,31 @@
       </c>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="16">
-        <f>IF(OR(A15="",I15="",I15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
+        <f>IF(OR(A15="",I15="",NOT(ISNUMBER(I15)),N(I15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF(OR(A15="",I15=""),"",IF(NOT(ISNUMBER(F15)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A15="",I15=""),"",IF(NOT(ISNUMBER(I15)),"Preço inválido",IF(NOT(ISNUMBER(F15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="16">
-        <f>IF(OR(A15="",L15="",L15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
+        <f>IF(OR(A15="",L15="",NOT(ISNUMBER(L15)),N(L15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
         <v/>
       </c>
       <c r="N15" s="15" t="n"/>
       <c r="O15" s="16">
-        <f>IF(OR(A15="",N15="",N15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
+        <f>IF(OR(A15="",N15="",NOT(ISNUMBER(N15)),N(N15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
         <v/>
       </c>
       <c r="P15" s="15" t="n"/>
       <c r="Q15" s="16">
-        <f>IF(OR(A15="",P15="",P15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
+        <f>IF(OR(A15="",P15="",NOT(ISNUMBER(P15)),N(P15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
         <v/>
       </c>
       <c r="R15" s="15" t="n"/>
       <c r="S15" s="16">
-        <f>IF(OR(A15="",R15="",R15=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
+        <f>IF(OR(A15="",R15="",NOT(ISNUMBER(R15)),N(R15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
         <v/>
       </c>
       <c r="T15" s="18">
@@ -2069,11 +2069,11 @@
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="12">
-        <f>IF(A16="","",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF(A16="","",IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>IF(A16="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",E16/60*Config!$B$7+D16))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(E16)),E16,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D16),AND(D16&gt;=0),FALSE)),"falta o material",E16/60*Config!$B$7+D16))))</f>
         <v/>
       </c>
       <c r="G16" s="14">
@@ -2086,31 +2086,31 @@
       </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="16">
-        <f>IF(OR(A16="",I16="",I16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
+        <f>IF(OR(A16="",I16="",NOT(ISNUMBER(I16)),N(I16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF(OR(A16="",I16=""),"",IF(NOT(ISNUMBER(F16)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A16="",I16=""),"",IF(NOT(ISNUMBER(I16)),"Preço inválido",IF(NOT(ISNUMBER(F16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="16">
-        <f>IF(OR(A16="",L16="",L16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
+        <f>IF(OR(A16="",L16="",NOT(ISNUMBER(L16)),N(L16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
         <v/>
       </c>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="16">
-        <f>IF(OR(A16="",N16="",N16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
+        <f>IF(OR(A16="",N16="",NOT(ISNUMBER(N16)),N(N16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
         <v/>
       </c>
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="16">
-        <f>IF(OR(A16="",P16="",P16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
+        <f>IF(OR(A16="",P16="",NOT(ISNUMBER(P16)),N(P16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
         <v/>
       </c>
       <c r="R16" s="15" t="n"/>
       <c r="S16" s="16">
-        <f>IF(OR(A16="",R16="",R16=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
+        <f>IF(OR(A16="",R16="",NOT(ISNUMBER(R16)),N(R16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
         <v/>
       </c>
       <c r="T16" s="18">
@@ -2177,7 +2177,7 @@
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="14">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",Config!$B$7/(1-Config!$B$8-Config!$B$9)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",Config!$B$7/(1-Config!$B$8-Config!$B$9))))</f>
         <v>338.983050847458</v>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="24" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16))))</f>
         <v>0 de 7</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="25">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",COUNTIF($T$5:$W$16,"&lt;0")))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($T$5:$W$16,"&lt;0"))))</f>
         <v>14</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="14">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",-MIN($T$5:$W$16)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",-MIN($T$5:$W$16))))</f>
         <v>60.4333333333333</v>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B35" s="12">
-        <f>B31+IF(B32="Sim",Config!$B$11*Config!$B$12,0)</f>
+        <f>IF(NOT(IF(ISNUMBER(B31),AND(B31&gt;=0),FALSE)),"faltam os minutos",IF(AND(B32&lt;&gt;"Sim",B32&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(B32="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B31+IF(B32="Sim",Config!$B$11*Config!$B$12,0))))</f>
         <v>53</v>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="B36" s="27">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",B35/60*Config!$B$7+B33)</f>
+        <f>IF(NOT(ISNUMBER(B35)),B35,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(B33),AND(B33&gt;=0),FALSE)),"falta o material",B35/60*Config!$B$7+B33)))</f>
         <v>180.666666666667</v>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="B39" s="16">
-        <f>IF(OR(B34=0,NOT(ISNUMBER(B36)),(Config!$B$13&lt;&gt;"Sim")),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
+        <f>IF(OR(NOT(ISNUMBER(B34)),N(B34)=0,NOT(ISNUMBER(B36)),(Config!$B$13&lt;&gt;"Sim")),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
         <v>0.513611111111111</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B40" s="28" t="str">
-        <f>IF(B34=0,"",IF(NOT(ISNUMBER(B36)),"Falta o custo-hora em Config",IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))</f>
+        <f>IF(B34="","",IF(NOT(ISNUMBER(B34)),"Preço pretendido inválido",IF(B34=0,"",IF(NOT(ISNUMBER(B36)),IF(ISNUMBER(Config!$B$7),"Faltam dados: "&amp;B36,"Falta o custo-hora em Config"),IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="C40" s="22" t="n"/>
@@ -2381,7 +2381,7 @@
   </mergeCells>
   <conditionalFormatting sqref="K5:K16">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(K5="Abaixo do mínimo",K5="Falta o custo-hora",K5="Margens inválidas")</formula>
+      <formula>OR(K5="Abaixo do mínimo",K5="Falta o custo-hora",K5="Margens inválidas",K5="Faltam dados da linha",K5="Preço inválido")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>K5="Entre mínimo e alvo"</formula>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1227,37 +1227,37 @@
         <v>380</v>
       </c>
       <c r="J5" s="16">
-        <f>IF(OR(A5="",I5="",NOT(ISNUMBER(I5)),N(I5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
+        <f>IF(OR(A5="",I5="",NOT(IF(ISNUMBER(I5),AND(I5&gt;=0),FALSE)),N(I5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(I5*(1-Config!$B$8)-F5)/I5)</f>
         <v>0.546140350877193</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IF(OR(A5="",I5=""),"",IF(NOT(ISNUMBER(I5)),"Preço inválido",IF(NOT(ISNUMBER(F5)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A5="",I5=""),"",IF(NOT(IF(ISNUMBER(I5),AND(I5&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F5)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L5" s="15" t="n">
         <v>120</v>
       </c>
       <c r="M5" s="16">
-        <f>IF(OR(A5="",L5="",NOT(ISNUMBER(L5)),N(L5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
+        <f>IF(OR(A5="",L5="",NOT(IF(ISNUMBER(L5),AND(L5&gt;=0),FALSE)),N(L5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(L5*(1-Config!$B$8)-F5)/L5)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>100</v>
       </c>
       <c r="O5" s="16">
-        <f>IF(OR(A5="",N5="",NOT(ISNUMBER(N5)),N(N5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
+        <f>IF(OR(A5="",N5="",NOT(IF(ISNUMBER(N5),AND(N5&gt;=0),FALSE)),N(N5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(N5*(1-Config!$B$8)-F5)/N5)</f>
         <v>-0.416666666666667</v>
       </c>
       <c r="P5" s="15" t="n">
         <v>90</v>
       </c>
       <c r="Q5" s="16">
-        <f>IF(OR(A5="",P5="",NOT(ISNUMBER(P5)),N(P5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
+        <f>IF(OR(A5="",P5="",NOT(IF(ISNUMBER(P5),AND(P5&gt;=0),FALSE)),N(P5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(P5*(1-Config!$B$8)-F5)/P5)</f>
         <v>-0.561851851851852</v>
       </c>
       <c r="R5" s="15" t="n"/>
       <c r="S5" s="16">
-        <f>IF(OR(A5="",R5="",NOT(ISNUMBER(R5)),N(R5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
+        <f>IF(OR(A5="",R5="",NOT(IF(ISNUMBER(R5),AND(R5&gt;=0),FALSE)),N(R5)=0,NOT(ISNUMBER(F5)),(Config!$B$13&lt;&gt;"Sim")),"",(R5*(1-Config!$B$8)-F5)/R5)</f>
         <v/>
       </c>
       <c r="T5" s="18">
@@ -1314,37 +1314,37 @@
         <v>0</v>
       </c>
       <c r="J6" s="16">
-        <f>IF(OR(A6="",I6="",NOT(ISNUMBER(I6)),N(I6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
+        <f>IF(OR(A6="",I6="",NOT(IF(ISNUMBER(I6),AND(I6&gt;=0),FALSE)),N(I6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(I6*(1-Config!$B$8)-F6)/I6)</f>
         <v/>
       </c>
       <c r="K6" s="17" t="str">
-        <f>IF(OR(A6="",I6=""),"",IF(NOT(ISNUMBER(I6)),"Preço inválido",IF(NOT(ISNUMBER(F6)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A6="",I6=""),"",IF(NOT(IF(ISNUMBER(I6),AND(I6&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F6)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="L6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f>IF(OR(A6="",L6="",NOT(ISNUMBER(L6)),N(L6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
+        <f>IF(OR(A6="",L6="",NOT(IF(ISNUMBER(L6),AND(L6&gt;=0),FALSE)),N(L6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(L6*(1-Config!$B$8)-F6)/L6)</f>
         <v/>
       </c>
       <c r="N6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="16">
-        <f>IF(OR(A6="",N6="",NOT(ISNUMBER(N6)),N(N6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
+        <f>IF(OR(A6="",N6="",NOT(IF(ISNUMBER(N6),AND(N6&gt;=0),FALSE)),N(N6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(N6*(1-Config!$B$8)-F6)/N6)</f>
         <v/>
       </c>
       <c r="P6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="16">
-        <f>IF(OR(A6="",P6="",NOT(ISNUMBER(P6)),N(P6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
+        <f>IF(OR(A6="",P6="",NOT(IF(ISNUMBER(P6),AND(P6&gt;=0),FALSE)),N(P6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(P6*(1-Config!$B$8)-F6)/P6)</f>
         <v/>
       </c>
       <c r="R6" s="15" t="n"/>
       <c r="S6" s="16">
-        <f>IF(OR(A6="",R6="",NOT(ISNUMBER(R6)),N(R6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
+        <f>IF(OR(A6="",R6="",NOT(IF(ISNUMBER(R6),AND(R6&gt;=0),FALSE)),N(R6)=0,NOT(ISNUMBER(F6)),(Config!$B$13&lt;&gt;"Sim")),"",(R6*(1-Config!$B$8)-F6)/R6)</f>
         <v/>
       </c>
       <c r="T6" s="18">
@@ -1401,37 +1401,37 @@
         <v>130</v>
       </c>
       <c r="J7" s="16">
-        <f>IF(OR(A7="",I7="",NOT(ISNUMBER(I7)),N(I7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
+        <f>IF(OR(A7="",I7="",NOT(IF(ISNUMBER(I7),AND(I7&gt;=0),FALSE)),N(I7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(I7*(1-Config!$B$8)-F7)/I7)</f>
         <v>0.315641025641026</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IF(OR(A7="",I7=""),"",IF(NOT(ISNUMBER(I7)),"Preço inválido",IF(NOT(ISNUMBER(F7)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A7="",I7=""),"",IF(NOT(IF(ISNUMBER(I7),AND(I7&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F7)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="L7" s="15" t="n">
         <v>40</v>
       </c>
       <c r="M7" s="16">
-        <f>IF(OR(A7="",L7="",NOT(ISNUMBER(L7)),N(L7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
+        <f>IF(OR(A7="",L7="",NOT(IF(ISNUMBER(L7),AND(L7&gt;=0),FALSE)),N(L7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(L7*(1-Config!$B$8)-F7)/L7)</f>
         <v>-0.976666666666666</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>35</v>
       </c>
       <c r="O7" s="16">
-        <f>IF(OR(A7="",N7="",NOT(ISNUMBER(N7)),N(N7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
+        <f>IF(OR(A7="",N7="",NOT(IF(ISNUMBER(N7),AND(N7&gt;=0),FALSE)),N(N7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(N7*(1-Config!$B$8)-F7)/N7)</f>
         <v>-1.24333333333333</v>
       </c>
       <c r="P7" s="15" t="n">
         <v>32</v>
       </c>
       <c r="Q7" s="16">
-        <f>IF(OR(A7="",P7="",NOT(ISNUMBER(P7)),N(P7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
+        <f>IF(OR(A7="",P7="",NOT(IF(ISNUMBER(P7),AND(P7&gt;=0),FALSE)),N(P7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(P7*(1-Config!$B$8)-F7)/P7)</f>
         <v>-1.44333333333333</v>
       </c>
       <c r="R7" s="15" t="n"/>
       <c r="S7" s="16">
-        <f>IF(OR(A7="",R7="",NOT(ISNUMBER(R7)),N(R7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
+        <f>IF(OR(A7="",R7="",NOT(IF(ISNUMBER(R7),AND(R7&gt;=0),FALSE)),N(R7)=0,NOT(ISNUMBER(F7)),(Config!$B$13&lt;&gt;"Sim")),"",(R7*(1-Config!$B$8)-F7)/R7)</f>
         <v/>
       </c>
       <c r="T7" s="18">
@@ -1488,37 +1488,37 @@
         <v>300</v>
       </c>
       <c r="J8" s="16">
-        <f>IF(OR(A8="",I8="",NOT(ISNUMBER(I8)),N(I8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
+        <f>IF(OR(A8="",I8="",NOT(IF(ISNUMBER(I8),AND(I8&gt;=0),FALSE)),N(I8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(I8*(1-Config!$B$8)-F8)/I8)</f>
         <v>0.617777777777778</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IF(OR(A8="",I8=""),"",IF(NOT(ISNUMBER(I8)),"Preço inválido",IF(NOT(ISNUMBER(F8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A8="",I8=""),"",IF(NOT(IF(ISNUMBER(I8),AND(I8&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L8" s="15" t="n">
         <v>95</v>
       </c>
       <c r="M8" s="16">
-        <f>IF(OR(A8="",L8="",NOT(ISNUMBER(L8)),N(L8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
+        <f>IF(OR(A8="",L8="",NOT(IF(ISNUMBER(L8),AND(L8&gt;=0),FALSE)),N(L8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(L8*(1-Config!$B$8)-F8)/L8)</f>
         <v>0.0303508771929825</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>85</v>
       </c>
       <c r="O8" s="16">
-        <f>IF(OR(A8="",N8="",NOT(ISNUMBER(N8)),N(N8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
+        <f>IF(OR(A8="",N8="",NOT(IF(ISNUMBER(N8),AND(N8&gt;=0),FALSE)),N(N8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(N8*(1-Config!$B$8)-F8)/N8)</f>
         <v>-0.07078431372549</v>
       </c>
       <c r="P8" s="15" t="n">
         <v>75</v>
       </c>
       <c r="Q8" s="16">
-        <f>IF(OR(A8="",P8="",NOT(ISNUMBER(P8)),N(P8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
+        <f>IF(OR(A8="",P8="",NOT(IF(ISNUMBER(P8),AND(P8&gt;=0),FALSE)),N(P8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(P8*(1-Config!$B$8)-F8)/P8)</f>
         <v>-0.198888888888889</v>
       </c>
       <c r="R8" s="15" t="n"/>
       <c r="S8" s="16">
-        <f>IF(OR(A8="",R8="",NOT(ISNUMBER(R8)),N(R8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
+        <f>IF(OR(A8="",R8="",NOT(IF(ISNUMBER(R8),AND(R8&gt;=0),FALSE)),N(R8)=0,NOT(ISNUMBER(F8)),(Config!$B$13&lt;&gt;"Sim")),"",(R8*(1-Config!$B$8)-F8)/R8)</f>
         <v/>
       </c>
       <c r="T8" s="18">
@@ -1575,37 +1575,37 @@
         <v>350</v>
       </c>
       <c r="J9" s="16">
-        <f>IF(OR(A9="",I9="",NOT(ISNUMBER(I9)),N(I9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
+        <f>IF(OR(A9="",I9="",NOT(IF(ISNUMBER(I9),AND(I9&gt;=0),FALSE)),N(I9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(I9*(1-Config!$B$8)-F9)/I9)</f>
         <v>0.648095238095238</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IF(OR(A9="",I9=""),"",IF(NOT(ISNUMBER(I9)),"Preço inválido",IF(NOT(ISNUMBER(F9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A9="",I9=""),"",IF(NOT(IF(ISNUMBER(I9),AND(I9&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L9" s="15" t="n">
         <v>105</v>
       </c>
       <c r="M9" s="16">
-        <f>IF(OR(A9="",L9="",NOT(ISNUMBER(L9)),N(L9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
+        <f>IF(OR(A9="",L9="",NOT(IF(ISNUMBER(L9),AND(L9&gt;=0),FALSE)),N(L9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(L9*(1-Config!$B$8)-F9)/L9)</f>
         <v>0.0836507936507938</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>95</v>
       </c>
       <c r="O9" s="16">
-        <f>IF(OR(A9="",N9="",NOT(ISNUMBER(N9)),N(N9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
+        <f>IF(OR(A9="",N9="",NOT(IF(ISNUMBER(N9),AND(N9&gt;=0),FALSE)),N(N9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(N9*(1-Config!$B$8)-F9)/N9)</f>
         <v>-0.00122807017543853</v>
       </c>
       <c r="P9" s="15" t="n">
         <v>85</v>
       </c>
       <c r="Q9" s="16">
-        <f>IF(OR(A9="",P9="",NOT(ISNUMBER(P9)),N(P9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
+        <f>IF(OR(A9="",P9="",NOT(IF(ISNUMBER(P9),AND(P9&gt;=0),FALSE)),N(P9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(P9*(1-Config!$B$8)-F9)/P9)</f>
         <v>-0.106078431372549</v>
       </c>
       <c r="R9" s="15" t="n"/>
       <c r="S9" s="16">
-        <f>IF(OR(A9="",R9="",NOT(ISNUMBER(R9)),N(R9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
+        <f>IF(OR(A9="",R9="",NOT(IF(ISNUMBER(R9),AND(R9&gt;=0),FALSE)),N(R9)=0,NOT(ISNUMBER(F9)),(Config!$B$13&lt;&gt;"Sim")),"",(R9*(1-Config!$B$8)-F9)/R9)</f>
         <v/>
       </c>
       <c r="T9" s="18">
@@ -1662,37 +1662,37 @@
         <v>450</v>
       </c>
       <c r="J10" s="16">
-        <f>IF(OR(A10="",I10="",NOT(ISNUMBER(I10)),N(I10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
+        <f>IF(OR(A10="",I10="",NOT(IF(ISNUMBER(I10),AND(I10&gt;=0),FALSE)),N(I10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(I10*(1-Config!$B$8)-F10)/I10)</f>
         <v>0.538148148148148</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IF(OR(A10="",I10=""),"",IF(NOT(ISNUMBER(I10)),"Preço inválido",IF(NOT(ISNUMBER(F10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A10="",I10=""),"",IF(NOT(IF(ISNUMBER(I10),AND(I10&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>140</v>
       </c>
       <c r="M10" s="16">
-        <f>IF(OR(A10="",L10="",NOT(ISNUMBER(L10)),N(L10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
+        <f>IF(OR(A10="",L10="",NOT(IF(ISNUMBER(L10),AND(L10&gt;=0),FALSE)),N(L10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(L10*(1-Config!$B$8)-F10)/L10)</f>
         <v>-0.240952380952381</v>
       </c>
       <c r="N10" s="15" t="n">
         <v>125</v>
       </c>
       <c r="O10" s="16">
-        <f>IF(OR(A10="",N10="",NOT(ISNUMBER(N10)),N(N10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
+        <f>IF(OR(A10="",N10="",NOT(IF(ISNUMBER(N10),AND(N10&gt;=0),FALSE)),N(N10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(N10*(1-Config!$B$8)-F10)/N10)</f>
         <v>-0.376666666666667</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>110</v>
       </c>
       <c r="Q10" s="16">
-        <f>IF(OR(A10="",P10="",NOT(ISNUMBER(P10)),N(P10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
+        <f>IF(OR(A10="",P10="",NOT(IF(ISNUMBER(P10),AND(P10&gt;=0),FALSE)),N(P10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(P10*(1-Config!$B$8)-F10)/P10)</f>
         <v>-0.549393939393939</v>
       </c>
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="16">
-        <f>IF(OR(A10="",R10="",NOT(ISNUMBER(R10)),N(R10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
+        <f>IF(OR(A10="",R10="",NOT(IF(ISNUMBER(R10),AND(R10&gt;=0),FALSE)),N(R10)=0,NOT(ISNUMBER(F10)),(Config!$B$13&lt;&gt;"Sim")),"",(R10*(1-Config!$B$8)-F10)/R10)</f>
         <v/>
       </c>
       <c r="T10" s="18">
@@ -1749,33 +1749,33 @@
         <v>400</v>
       </c>
       <c r="J11" s="16">
-        <f>IF(OR(A11="",I11="",NOT(ISNUMBER(I11)),N(I11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
+        <f>IF(OR(A11="",I11="",NOT(IF(ISNUMBER(I11),AND(I11&gt;=0),FALSE)),N(I11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(I11*(1-Config!$B$8)-F11)/I11)</f>
         <v>0.48</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IF(OR(A11="",I11=""),"",IF(NOT(ISNUMBER(I11)),"Preço inválido",IF(NOT(ISNUMBER(F11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A11="",I11=""),"",IF(NOT(IF(ISNUMBER(I11),AND(I11&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L11" s="15" t="n">
         <v>130</v>
       </c>
       <c r="M11" s="16">
-        <f>IF(OR(A11="",L11="",NOT(ISNUMBER(L11)),N(L11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
+        <f>IF(OR(A11="",L11="",NOT(IF(ISNUMBER(L11),AND(L11&gt;=0),FALSE)),N(L11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(L11*(1-Config!$B$8)-F11)/L11)</f>
         <v>-0.371538461538462</v>
       </c>
       <c r="N11" s="15" t="n"/>
       <c r="O11" s="16">
-        <f>IF(OR(A11="",N11="",NOT(ISNUMBER(N11)),N(N11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
+        <f>IF(OR(A11="",N11="",NOT(IF(ISNUMBER(N11),AND(N11&gt;=0),FALSE)),N(N11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(N11*(1-Config!$B$8)-F11)/N11)</f>
         <v/>
       </c>
       <c r="P11" s="15" t="n"/>
       <c r="Q11" s="16">
-        <f>IF(OR(A11="",P11="",NOT(ISNUMBER(P11)),N(P11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
+        <f>IF(OR(A11="",P11="",NOT(IF(ISNUMBER(P11),AND(P11&gt;=0),FALSE)),N(P11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(P11*(1-Config!$B$8)-F11)/P11)</f>
         <v/>
       </c>
       <c r="R11" s="15" t="n"/>
       <c r="S11" s="16">
-        <f>IF(OR(A11="",R11="",NOT(ISNUMBER(R11)),N(R11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
+        <f>IF(OR(A11="",R11="",NOT(IF(ISNUMBER(R11),AND(R11&gt;=0),FALSE)),N(R11)=0,NOT(ISNUMBER(F11)),(Config!$B$13&lt;&gt;"Sim")),"",(R11*(1-Config!$B$8)-F11)/R11)</f>
         <v/>
       </c>
       <c r="T11" s="18">
@@ -1818,31 +1818,31 @@
       </c>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="16">
-        <f>IF(OR(A12="",I12="",NOT(ISNUMBER(I12)),N(I12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
+        <f>IF(OR(A12="",I12="",NOT(IF(ISNUMBER(I12),AND(I12&gt;=0),FALSE)),N(I12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(I12*(1-Config!$B$8)-F12)/I12)</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF(OR(A12="",I12=""),"",IF(NOT(ISNUMBER(I12)),"Preço inválido",IF(NOT(ISNUMBER(F12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A12="",I12=""),"",IF(NOT(IF(ISNUMBER(I12),AND(I12&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="16">
-        <f>IF(OR(A12="",L12="",NOT(ISNUMBER(L12)),N(L12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
+        <f>IF(OR(A12="",L12="",NOT(IF(ISNUMBER(L12),AND(L12&gt;=0),FALSE)),N(L12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(L12*(1-Config!$B$8)-F12)/L12)</f>
         <v/>
       </c>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="16">
-        <f>IF(OR(A12="",N12="",NOT(ISNUMBER(N12)),N(N12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
+        <f>IF(OR(A12="",N12="",NOT(IF(ISNUMBER(N12),AND(N12&gt;=0),FALSE)),N(N12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(N12*(1-Config!$B$8)-F12)/N12)</f>
         <v/>
       </c>
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="16">
-        <f>IF(OR(A12="",P12="",NOT(ISNUMBER(P12)),N(P12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
+        <f>IF(OR(A12="",P12="",NOT(IF(ISNUMBER(P12),AND(P12&gt;=0),FALSE)),N(P12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(P12*(1-Config!$B$8)-F12)/P12)</f>
         <v/>
       </c>
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="16">
-        <f>IF(OR(A12="",R12="",NOT(ISNUMBER(R12)),N(R12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
+        <f>IF(OR(A12="",R12="",NOT(IF(ISNUMBER(R12),AND(R12&gt;=0),FALSE)),N(R12)=0,NOT(ISNUMBER(F12)),(Config!$B$13&lt;&gt;"Sim")),"",(R12*(1-Config!$B$8)-F12)/R12)</f>
         <v/>
       </c>
       <c r="T12" s="18">
@@ -1885,31 +1885,31 @@
       </c>
       <c r="I13" s="15" t="n"/>
       <c r="J13" s="16">
-        <f>IF(OR(A13="",I13="",NOT(ISNUMBER(I13)),N(I13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
+        <f>IF(OR(A13="",I13="",NOT(IF(ISNUMBER(I13),AND(I13&gt;=0),FALSE)),N(I13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(I13*(1-Config!$B$8)-F13)/I13)</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF(OR(A13="",I13=""),"",IF(NOT(ISNUMBER(I13)),"Preço inválido",IF(NOT(ISNUMBER(F13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A13="",I13=""),"",IF(NOT(IF(ISNUMBER(I13),AND(I13&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="16">
-        <f>IF(OR(A13="",L13="",NOT(ISNUMBER(L13)),N(L13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
+        <f>IF(OR(A13="",L13="",NOT(IF(ISNUMBER(L13),AND(L13&gt;=0),FALSE)),N(L13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(L13*(1-Config!$B$8)-F13)/L13)</f>
         <v/>
       </c>
       <c r="N13" s="15" t="n"/>
       <c r="O13" s="16">
-        <f>IF(OR(A13="",N13="",NOT(ISNUMBER(N13)),N(N13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
+        <f>IF(OR(A13="",N13="",NOT(IF(ISNUMBER(N13),AND(N13&gt;=0),FALSE)),N(N13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(N13*(1-Config!$B$8)-F13)/N13)</f>
         <v/>
       </c>
       <c r="P13" s="15" t="n"/>
       <c r="Q13" s="16">
-        <f>IF(OR(A13="",P13="",NOT(ISNUMBER(P13)),N(P13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
+        <f>IF(OR(A13="",P13="",NOT(IF(ISNUMBER(P13),AND(P13&gt;=0),FALSE)),N(P13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(P13*(1-Config!$B$8)-F13)/P13)</f>
         <v/>
       </c>
       <c r="R13" s="15" t="n"/>
       <c r="S13" s="16">
-        <f>IF(OR(A13="",R13="",NOT(ISNUMBER(R13)),N(R13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
+        <f>IF(OR(A13="",R13="",NOT(IF(ISNUMBER(R13),AND(R13&gt;=0),FALSE)),N(R13)=0,NOT(ISNUMBER(F13)),(Config!$B$13&lt;&gt;"Sim")),"",(R13*(1-Config!$B$8)-F13)/R13)</f>
         <v/>
       </c>
       <c r="T13" s="18">
@@ -1952,31 +1952,31 @@
       </c>
       <c r="I14" s="15" t="n"/>
       <c r="J14" s="16">
-        <f>IF(OR(A14="",I14="",NOT(ISNUMBER(I14)),N(I14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
+        <f>IF(OR(A14="",I14="",NOT(IF(ISNUMBER(I14),AND(I14&gt;=0),FALSE)),N(I14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(I14*(1-Config!$B$8)-F14)/I14)</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF(OR(A14="",I14=""),"",IF(NOT(ISNUMBER(I14)),"Preço inválido",IF(NOT(ISNUMBER(F14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A14="",I14=""),"",IF(NOT(IF(ISNUMBER(I14),AND(I14&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="16">
-        <f>IF(OR(A14="",L14="",NOT(ISNUMBER(L14)),N(L14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
+        <f>IF(OR(A14="",L14="",NOT(IF(ISNUMBER(L14),AND(L14&gt;=0),FALSE)),N(L14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(L14*(1-Config!$B$8)-F14)/L14)</f>
         <v/>
       </c>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="16">
-        <f>IF(OR(A14="",N14="",NOT(ISNUMBER(N14)),N(N14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
+        <f>IF(OR(A14="",N14="",NOT(IF(ISNUMBER(N14),AND(N14&gt;=0),FALSE)),N(N14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(N14*(1-Config!$B$8)-F14)/N14)</f>
         <v/>
       </c>
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="16">
-        <f>IF(OR(A14="",P14="",NOT(ISNUMBER(P14)),N(P14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
+        <f>IF(OR(A14="",P14="",NOT(IF(ISNUMBER(P14),AND(P14&gt;=0),FALSE)),N(P14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(P14*(1-Config!$B$8)-F14)/P14)</f>
         <v/>
       </c>
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="16">
-        <f>IF(OR(A14="",R14="",NOT(ISNUMBER(R14)),N(R14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
+        <f>IF(OR(A14="",R14="",NOT(IF(ISNUMBER(R14),AND(R14&gt;=0),FALSE)),N(R14)=0,NOT(ISNUMBER(F14)),(Config!$B$13&lt;&gt;"Sim")),"",(R14*(1-Config!$B$8)-F14)/R14)</f>
         <v/>
       </c>
       <c r="T14" s="18">
@@ -2019,31 +2019,31 @@
       </c>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="16">
-        <f>IF(OR(A15="",I15="",NOT(ISNUMBER(I15)),N(I15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
+        <f>IF(OR(A15="",I15="",NOT(IF(ISNUMBER(I15),AND(I15&gt;=0),FALSE)),N(I15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(I15*(1-Config!$B$8)-F15)/I15)</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF(OR(A15="",I15=""),"",IF(NOT(ISNUMBER(I15)),"Preço inválido",IF(NOT(ISNUMBER(F15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A15="",I15=""),"",IF(NOT(IF(ISNUMBER(I15),AND(I15&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="16">
-        <f>IF(OR(A15="",L15="",NOT(ISNUMBER(L15)),N(L15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
+        <f>IF(OR(A15="",L15="",NOT(IF(ISNUMBER(L15),AND(L15&gt;=0),FALSE)),N(L15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(L15*(1-Config!$B$8)-F15)/L15)</f>
         <v/>
       </c>
       <c r="N15" s="15" t="n"/>
       <c r="O15" s="16">
-        <f>IF(OR(A15="",N15="",NOT(ISNUMBER(N15)),N(N15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
+        <f>IF(OR(A15="",N15="",NOT(IF(ISNUMBER(N15),AND(N15&gt;=0),FALSE)),N(N15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(N15*(1-Config!$B$8)-F15)/N15)</f>
         <v/>
       </c>
       <c r="P15" s="15" t="n"/>
       <c r="Q15" s="16">
-        <f>IF(OR(A15="",P15="",NOT(ISNUMBER(P15)),N(P15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
+        <f>IF(OR(A15="",P15="",NOT(IF(ISNUMBER(P15),AND(P15&gt;=0),FALSE)),N(P15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(P15*(1-Config!$B$8)-F15)/P15)</f>
         <v/>
       </c>
       <c r="R15" s="15" t="n"/>
       <c r="S15" s="16">
-        <f>IF(OR(A15="",R15="",NOT(ISNUMBER(R15)),N(R15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
+        <f>IF(OR(A15="",R15="",NOT(IF(ISNUMBER(R15),AND(R15&gt;=0),FALSE)),N(R15)=0,NOT(ISNUMBER(F15)),(Config!$B$13&lt;&gt;"Sim")),"",(R15*(1-Config!$B$8)-F15)/R15)</f>
         <v/>
       </c>
       <c r="T15" s="18">
@@ -2086,31 +2086,31 @@
       </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="16">
-        <f>IF(OR(A16="",I16="",NOT(ISNUMBER(I16)),N(I16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
+        <f>IF(OR(A16="",I16="",NOT(IF(ISNUMBER(I16),AND(I16&gt;=0),FALSE)),N(I16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(I16*(1-Config!$B$8)-F16)/I16)</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF(OR(A16="",I16=""),"",IF(NOT(ISNUMBER(I16)),"Preço inválido",IF(NOT(ISNUMBER(F16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A16="",I16=""),"",IF(NOT(IF(ISNUMBER(I16),AND(I16&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="16">
-        <f>IF(OR(A16="",L16="",NOT(ISNUMBER(L16)),N(L16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
+        <f>IF(OR(A16="",L16="",NOT(IF(ISNUMBER(L16),AND(L16&gt;=0),FALSE)),N(L16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(L16*(1-Config!$B$8)-F16)/L16)</f>
         <v/>
       </c>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="16">
-        <f>IF(OR(A16="",N16="",NOT(ISNUMBER(N16)),N(N16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
+        <f>IF(OR(A16="",N16="",NOT(IF(ISNUMBER(N16),AND(N16&gt;=0),FALSE)),N(N16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(N16*(1-Config!$B$8)-F16)/N16)</f>
         <v/>
       </c>
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="16">
-        <f>IF(OR(A16="",P16="",NOT(ISNUMBER(P16)),N(P16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
+        <f>IF(OR(A16="",P16="",NOT(IF(ISNUMBER(P16),AND(P16&gt;=0),FALSE)),N(P16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(P16*(1-Config!$B$8)-F16)/P16)</f>
         <v/>
       </c>
       <c r="R16" s="15" t="n"/>
       <c r="S16" s="16">
-        <f>IF(OR(A16="",R16="",NOT(ISNUMBER(R16)),N(R16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
+        <f>IF(OR(A16="",R16="",NOT(IF(ISNUMBER(R16),AND(R16&gt;=0),FALSE)),N(R16)=0,NOT(ISNUMBER(F16)),(Config!$B$13&lt;&gt;"Sim")),"",(R16*(1-Config!$B$8)-F16)/R16)</f>
         <v/>
       </c>
       <c r="T16" s="18">
@@ -2177,7 +2177,7 @@
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="14">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",Config!$B$7/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",Config!$B$7/(1-Config!$B$8-Config!$B$9))))</f>
         <v>338.983050847458</v>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="24" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16))))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16))))</f>
         <v>0 de 7</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="25">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($T$5:$W$16,"&lt;0"))))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($T$5:$W$16,"&lt;0"))))</f>
         <v>14</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="14">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(ISTEXT($I$5:$I$16)*1)+SUMPRODUCT(ISTEXT($L$5:$L$16)*1)+SUMPRODUCT(ISTEXT($N$5:$N$16)*1)+SUMPRODUCT(ISTEXT($P$5:$P$16)*1)+SUMPRODUCT(ISTEXT($R$5:$R$16)*1))&amp;" linha(s) ou preço(s) incompletos",-MIN($T$5:$W$16))))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",-MIN($T$5:$W$16))))</f>
         <v>60.4333333333333</v>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="B39" s="16">
-        <f>IF(OR(NOT(ISNUMBER(B34)),N(B34)=0,NOT(ISNUMBER(B36)),(Config!$B$13&lt;&gt;"Sim")),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B34),AND(B34&gt;=0),FALSE)),N(B34)=0,NOT(ISNUMBER(B36)),(Config!$B$13&lt;&gt;"Sim")),"",(B34*(1-Config!$B$8)-B36)/B34)</f>
         <v>0.513611111111111</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B40" s="28" t="str">
-        <f>IF(B34="","",IF(NOT(ISNUMBER(B34)),"Preço pretendido inválido",IF(B34=0,"",IF(NOT(ISNUMBER(B36)),IF(ISNUMBER(Config!$B$7),"Faltam dados: "&amp;B36,"Falta o custo-hora em Config"),IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))))</f>
+        <f>IF(B34="","",IF(NOT(IF(ISNUMBER(B34),AND(B34&gt;=0),FALSE)),"Preço pretendido inválido",IF(B34=0,"",IF(NOT(ISNUMBER(B36)),IF(ISNUMBER(Config!$B$7),"Faltam dados: "&amp;B36,"Falta o custo-hora em Config"),IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="C40" s="22" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1212,7 +1212,7 @@
         <v>38</v>
       </c>
       <c r="F5" s="13">
-        <f>IF(A5="","",IF(NOT(ISNUMBER(E5)),E5,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D5),AND(D5&gt;=0),FALSE)),"falta o material",E5/60*Config!$B$7+D5))))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(E5)),E5,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D5),AND(D5&gt;=0),FALSE)),"falta o material",E5/60*Config!$B$7+D5))))</f>
         <v>130.666666666667</v>
       </c>
       <c r="G5" s="14">
@@ -1231,7 +1231,7 @@
         <v>0.546140350877193</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IF(OR(A5="",I5=""),"",IF(NOT(IF(ISNUMBER(I5),AND(I5&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F5)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A5="","",IF(I5="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I5),AND(I5&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F5)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"Margens inválidas",IF(I5=0,"Sem cobrança",IF(I5&lt;G5,"Abaixo do mínimo",IF(I5&lt;H5,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L5" s="15" t="n">
@@ -1261,19 +1261,19 @@
         <v/>
       </c>
       <c r="T5" s="18">
-        <f>IF(AND(ISNUMBER(M5),M5&lt;0),M5*L5,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",L5&lt;&gt;"",IF(ISNUMBER(L5),AND(L5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L5&gt;0,N(I5)&gt;0)),MIN(0,L5*(1-Config!$B$8)-F5),0)</f>
         <v>-23.8666666666667</v>
       </c>
       <c r="U5" s="18">
-        <f>IF(AND(ISNUMBER(O5),O5&lt;0),O5*N5,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",N5&lt;&gt;"",IF(ISNUMBER(N5),AND(N5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N5&gt;0,N(I5)&gt;0)),MIN(0,N5*(1-Config!$B$8)-F5),0)</f>
         <v>-41.6666666666667</v>
       </c>
       <c r="V5" s="18">
-        <f>IF(AND(ISNUMBER(Q5),Q5&lt;0),Q5*P5,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",P5&lt;&gt;"",IF(ISNUMBER(P5),AND(P5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P5&gt;0,N(I5)&gt;0)),MIN(0,P5*(1-Config!$B$8)-F5),0)</f>
         <v>-50.5666666666667</v>
       </c>
       <c r="W5" s="18">
-        <f>IF(AND(ISNUMBER(S5),S5&lt;0),S5*R5,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",R5&lt;&gt;"",IF(ISNUMBER(R5),AND(R5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R5&gt;0,N(I5)&gt;0)),MIN(0,R5*(1-Config!$B$8)-F5),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="13">
-        <f>IF(A6="","",IF(NOT(ISNUMBER(E6)),E6,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D6),AND(D6&gt;=0),FALSE)),"falta o material",E6/60*Config!$B$7+D6))))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(E6)),E6,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D6),AND(D6&gt;=0),FALSE)),"falta o material",E6/60*Config!$B$7+D6))))</f>
         <v>68.6666666666667</v>
       </c>
       <c r="G6" s="14">
@@ -1318,7 +1318,7 @@
         <v/>
       </c>
       <c r="K6" s="17" t="str">
-        <f>IF(OR(A6="",I6=""),"",IF(NOT(IF(ISNUMBER(I6),AND(I6&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F6)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A6="","",IF(I6="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I6),AND(I6&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F6)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"Margens inválidas",IF(I6=0,"Sem cobrança",IF(I6&lt;G6,"Abaixo do mínimo",IF(I6&lt;H6,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="L6" s="15" t="n">
@@ -1348,19 +1348,19 @@
         <v/>
       </c>
       <c r="T6" s="18">
-        <f>IF(AND(ISNUMBER(M6),M6&lt;0),M6*L6,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",L6&lt;&gt;"",IF(ISNUMBER(L6),AND(L6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L6&gt;0,N(I6)&gt;0)),MIN(0,L6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
       <c r="U6" s="18">
-        <f>IF(AND(ISNUMBER(O6),O6&lt;0),O6*N6,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",N6&lt;&gt;"",IF(ISNUMBER(N6),AND(N6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N6&gt;0,N(I6)&gt;0)),MIN(0,N6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
       <c r="V6" s="18">
-        <f>IF(AND(ISNUMBER(Q6),Q6&lt;0),Q6*P6,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",P6&lt;&gt;"",IF(ISNUMBER(P6),AND(P6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P6&gt;0,N(I6)&gt;0)),MIN(0,P6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="18">
-        <f>IF(AND(ISNUMBER(S6),S6&lt;0),S6*R6,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",R6&lt;&gt;"",IF(ISNUMBER(R6),AND(R6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R6&gt;0,N(I6)&gt;0)),MIN(0,R6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="13">
-        <f>IF(A7="","",IF(NOT(ISNUMBER(E7)),E7,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D7),AND(D7&gt;=0),FALSE)),"falta o material",E7/60*Config!$B$7+D7))))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(E7)),E7,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D7),AND(D7&gt;=0),FALSE)),"falta o material",E7/60*Config!$B$7+D7))))</f>
         <v>74.6666666666667</v>
       </c>
       <c r="G7" s="14">
@@ -1405,7 +1405,7 @@
         <v>0.315641025641026</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IF(OR(A7="",I7=""),"",IF(NOT(IF(ISNUMBER(I7),AND(I7&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F7)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A7="","",IF(I7="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I7),AND(I7&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F7)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"Margens inválidas",IF(I7=0,"Sem cobrança",IF(I7&lt;G7,"Abaixo do mínimo",IF(I7&lt;H7,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="L7" s="15" t="n">
@@ -1435,19 +1435,19 @@
         <v/>
       </c>
       <c r="T7" s="18">
-        <f>IF(AND(ISNUMBER(M7),M7&lt;0),M7*L7,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",L7&lt;&gt;"",IF(ISNUMBER(L7),AND(L7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L7&gt;0,N(I7)&gt;0)),MIN(0,L7*(1-Config!$B$8)-F7),0)</f>
         <v>-39.0666666666667</v>
       </c>
       <c r="U7" s="18">
-        <f>IF(AND(ISNUMBER(O7),O7&lt;0),O7*N7,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",N7&lt;&gt;"",IF(ISNUMBER(N7),AND(N7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N7&gt;0,N(I7)&gt;0)),MIN(0,N7*(1-Config!$B$8)-F7),0)</f>
         <v>-43.5166666666667</v>
       </c>
       <c r="V7" s="18">
-        <f>IF(AND(ISNUMBER(Q7),Q7&lt;0),Q7*P7,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",P7&lt;&gt;"",IF(ISNUMBER(P7),AND(P7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P7&gt;0,N(I7)&gt;0)),MIN(0,P7*(1-Config!$B$8)-F7),0)</f>
         <v>-46.1866666666667</v>
       </c>
       <c r="W7" s="18">
-        <f>IF(AND(ISNUMBER(S7),S7&lt;0),S7*R7,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",R7&lt;&gt;"",IF(ISNUMBER(R7),AND(R7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R7&gt;0,N(I7)&gt;0)),MIN(0,R7*(1-Config!$B$8)-F7),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="13">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(E8)),E8,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D8),AND(D8&gt;=0),FALSE)),"falta o material",E8/60*Config!$B$7+D8))))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(E8)),E8,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D8),AND(D8&gt;=0),FALSE)),"falta o material",E8/60*Config!$B$7+D8))))</f>
         <v>81.6666666666667</v>
       </c>
       <c r="G8" s="14">
@@ -1492,7 +1492,7 @@
         <v>0.617777777777778</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IF(OR(A8="",I8=""),"",IF(NOT(IF(ISNUMBER(I8),AND(I8&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A8="","",IF(I8="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I8),AND(I8&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F8)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"Margens inválidas",IF(I8=0,"Sem cobrança",IF(I8&lt;G8,"Abaixo do mínimo",IF(I8&lt;H8,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L8" s="15" t="n">
@@ -1522,19 +1522,19 @@
         <v/>
       </c>
       <c r="T8" s="18">
-        <f>IF(AND(ISNUMBER(M8),M8&lt;0),M8*L8,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",L8&lt;&gt;"",IF(ISNUMBER(L8),AND(L8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L8&gt;0,N(I8)&gt;0)),MIN(0,L8*(1-Config!$B$8)-F8),0)</f>
         <v>0</v>
       </c>
       <c r="U8" s="18">
-        <f>IF(AND(ISNUMBER(O8),O8&lt;0),O8*N8,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",N8&lt;&gt;"",IF(ISNUMBER(N8),AND(N8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N8&gt;0,N(I8)&gt;0)),MIN(0,N8*(1-Config!$B$8)-F8),0)</f>
         <v>-6.01666666666665</v>
       </c>
       <c r="V8" s="18">
-        <f>IF(AND(ISNUMBER(Q8),Q8&lt;0),Q8*P8,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",P8&lt;&gt;"",IF(ISNUMBER(P8),AND(P8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P8&gt;0,N(I8)&gt;0)),MIN(0,P8*(1-Config!$B$8)-F8),0)</f>
         <v>-14.9166666666667</v>
       </c>
       <c r="W8" s="18">
-        <f>IF(AND(ISNUMBER(S8),S8&lt;0),S8*R8,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",R8&lt;&gt;"",IF(ISNUMBER(R8),AND(R8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R8&gt;0,N(I8)&gt;0)),MIN(0,R8*(1-Config!$B$8)-F8),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="13">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(E9)),E9,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D9),AND(D9&gt;=0),FALSE)),"falta o material",E9/60*Config!$B$7+D9))))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(E9)),E9,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D9),AND(D9&gt;=0),FALSE)),"falta o material",E9/60*Config!$B$7+D9))))</f>
         <v>84.6666666666667</v>
       </c>
       <c r="G9" s="14">
@@ -1579,7 +1579,7 @@
         <v>0.648095238095238</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IF(OR(A9="",I9=""),"",IF(NOT(IF(ISNUMBER(I9),AND(I9&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A9="","",IF(I9="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I9),AND(I9&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F9)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"Margens inválidas",IF(I9=0,"Sem cobrança",IF(I9&lt;G9,"Abaixo do mínimo",IF(I9&lt;H9,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L9" s="15" t="n">
@@ -1609,19 +1609,19 @@
         <v/>
       </c>
       <c r="T9" s="18">
-        <f>IF(AND(ISNUMBER(M9),M9&lt;0),M9*L9,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",L9&lt;&gt;"",IF(ISNUMBER(L9),AND(L9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L9&gt;0,N(I9)&gt;0)),MIN(0,L9*(1-Config!$B$8)-F9),0)</f>
         <v>0</v>
       </c>
       <c r="U9" s="18">
-        <f>IF(AND(ISNUMBER(O9),O9&lt;0),O9*N9,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",N9&lt;&gt;"",IF(ISNUMBER(N9),AND(N9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N9&gt;0,N(I9)&gt;0)),MIN(0,N9*(1-Config!$B$8)-F9),0)</f>
         <v>-0.11666666666666</v>
       </c>
       <c r="V9" s="18">
-        <f>IF(AND(ISNUMBER(Q9),Q9&lt;0),Q9*P9,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",P9&lt;&gt;"",IF(ISNUMBER(P9),AND(P9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P9&gt;0,N(I9)&gt;0)),MIN(0,P9*(1-Config!$B$8)-F9),0)</f>
         <v>-9.01666666666665</v>
       </c>
       <c r="W9" s="18">
-        <f>IF(AND(ISNUMBER(S9),S9&lt;0),S9*R9,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",R9&lt;&gt;"",IF(ISNUMBER(R9),AND(R9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R9&gt;0,N(I9)&gt;0)),MIN(0,R9*(1-Config!$B$8)-F9),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="13">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(E10)),E10,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D10),AND(D10&gt;=0),FALSE)),"falta o material",E10/60*Config!$B$7+D10))))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(E10)),E10,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D10),AND(D10&gt;=0),FALSE)),"falta o material",E10/60*Config!$B$7+D10))))</f>
         <v>158.333333333333</v>
       </c>
       <c r="G10" s="14">
@@ -1666,7 +1666,7 @@
         <v>0.538148148148148</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IF(OR(A10="",I10=""),"",IF(NOT(IF(ISNUMBER(I10),AND(I10&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A10="","",IF(I10="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I10),AND(I10&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F10)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"Margens inválidas",IF(I10=0,"Sem cobrança",IF(I10&lt;G10,"Abaixo do mínimo",IF(I10&lt;H10,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L10" s="15" t="n">
@@ -1696,19 +1696,19 @@
         <v/>
       </c>
       <c r="T10" s="18">
-        <f>IF(AND(ISNUMBER(M10),M10&lt;0),M10*L10,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",L10&lt;&gt;"",IF(ISNUMBER(L10),AND(L10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L10&gt;0,N(I10)&gt;0)),MIN(0,L10*(1-Config!$B$8)-F10),0)</f>
         <v>-33.7333333333333</v>
       </c>
       <c r="U10" s="18">
-        <f>IF(AND(ISNUMBER(O10),O10&lt;0),O10*N10,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",N10&lt;&gt;"",IF(ISNUMBER(N10),AND(N10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N10&gt;0,N(I10)&gt;0)),MIN(0,N10*(1-Config!$B$8)-F10),0)</f>
         <v>-47.0833333333333</v>
       </c>
       <c r="V10" s="18">
-        <f>IF(AND(ISNUMBER(Q10),Q10&lt;0),Q10*P10,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",P10&lt;&gt;"",IF(ISNUMBER(P10),AND(P10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P10&gt;0,N(I10)&gt;0)),MIN(0,P10*(1-Config!$B$8)-F10),0)</f>
         <v>-60.4333333333333</v>
       </c>
       <c r="W10" s="18">
-        <f>IF(AND(ISNUMBER(S10),S10&lt;0),S10*R10,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",R10&lt;&gt;"",IF(ISNUMBER(R10),AND(R10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R10&gt;0,N(I10)&gt;0)),MIN(0,R10*(1-Config!$B$8)-F10),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="13">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(E11)),E11,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D11),AND(D11&gt;=0),FALSE)),"falta o material",E11/60*Config!$B$7+D11))))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(E11)),E11,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D11),AND(D11&gt;=0),FALSE)),"falta o material",E11/60*Config!$B$7+D11))))</f>
         <v>164</v>
       </c>
       <c r="G11" s="14">
@@ -1753,7 +1753,7 @@
         <v>0.48</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IF(OR(A11="",I11=""),"",IF(NOT(IF(ISNUMBER(I11),AND(I11&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A11="","",IF(I11="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I11),AND(I11&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F11)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"Margens inválidas",IF(I11=0,"Sem cobrança",IF(I11&lt;G11,"Abaixo do mínimo",IF(I11&lt;H11,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="L11" s="15" t="n">
@@ -1779,19 +1779,19 @@
         <v/>
       </c>
       <c r="T11" s="18">
-        <f>IF(AND(ISNUMBER(M11),M11&lt;0),M11*L11,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",L11&lt;&gt;"",IF(ISNUMBER(L11),AND(L11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L11&gt;0,N(I11)&gt;0)),MIN(0,L11*(1-Config!$B$8)-F11),0)</f>
         <v>-48.3</v>
       </c>
       <c r="U11" s="18">
-        <f>IF(AND(ISNUMBER(O11),O11&lt;0),O11*N11,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",N11&lt;&gt;"",IF(ISNUMBER(N11),AND(N11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N11&gt;0,N(I11)&gt;0)),MIN(0,N11*(1-Config!$B$8)-F11),0)</f>
         <v>0</v>
       </c>
       <c r="V11" s="18">
-        <f>IF(AND(ISNUMBER(Q11),Q11&lt;0),Q11*P11,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",P11&lt;&gt;"",IF(ISNUMBER(P11),AND(P11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P11&gt;0,N(I11)&gt;0)),MIN(0,P11*(1-Config!$B$8)-F11),0)</f>
         <v>0</v>
       </c>
       <c r="W11" s="18">
-        <f>IF(AND(ISNUMBER(S11),S11&lt;0),S11*R11,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",R11&lt;&gt;"",IF(ISNUMBER(R11),AND(R11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R11&gt;0,N(I11)&gt;0)),MIN(0,R11*(1-Config!$B$8)-F11),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(E12)),E12,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D12),AND(D12&gt;=0),FALSE)),"falta o material",E12/60*Config!$B$7+D12))))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(E12)),E12,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D12),AND(D12&gt;=0),FALSE)),"falta o material",E12/60*Config!$B$7+D12))))</f>
         <v/>
       </c>
       <c r="G12" s="14">
@@ -1822,7 +1822,7 @@
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF(OR(A12="",I12=""),"",IF(NOT(IF(ISNUMBER(I12),AND(I12&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A12="","",IF(I12="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I12),AND(I12&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F12)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"Margens inválidas",IF(I12=0,"Sem cobrança",IF(I12&lt;G12,"Abaixo do mínimo",IF(I12&lt;H12,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -1846,19 +1846,19 @@
         <v/>
       </c>
       <c r="T12" s="18">
-        <f>IF(AND(ISNUMBER(M12),M12&lt;0),M12*L12,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",L12&lt;&gt;"",IF(ISNUMBER(L12),AND(L12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L12&gt;0,N(I12)&gt;0)),MIN(0,L12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
       <c r="U12" s="18">
-        <f>IF(AND(ISNUMBER(O12),O12&lt;0),O12*N12,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",N12&lt;&gt;"",IF(ISNUMBER(N12),AND(N12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N12&gt;0,N(I12)&gt;0)),MIN(0,N12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
       <c r="V12" s="18">
-        <f>IF(AND(ISNUMBER(Q12),Q12&lt;0),Q12*P12,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",P12&lt;&gt;"",IF(ISNUMBER(P12),AND(P12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P12&gt;0,N(I12)&gt;0)),MIN(0,P12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
       <c r="W12" s="18">
-        <f>IF(AND(ISNUMBER(S12),S12&lt;0),S12*R12,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",R12&lt;&gt;"",IF(ISNUMBER(R12),AND(R12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R12&gt;0,N(I12)&gt;0)),MIN(0,R12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(E13)),E13,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D13),AND(D13&gt;=0),FALSE)),"falta o material",E13/60*Config!$B$7+D13))))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(E13)),E13,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D13),AND(D13&gt;=0),FALSE)),"falta o material",E13/60*Config!$B$7+D13))))</f>
         <v/>
       </c>
       <c r="G13" s="14">
@@ -1889,7 +1889,7 @@
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF(OR(A13="",I13=""),"",IF(NOT(IF(ISNUMBER(I13),AND(I13&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A13="","",IF(I13="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I13),AND(I13&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F13)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"Margens inválidas",IF(I13=0,"Sem cobrança",IF(I13&lt;G13,"Abaixo do mínimo",IF(I13&lt;H13,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="L13" s="15" t="n"/>
@@ -1913,19 +1913,19 @@
         <v/>
       </c>
       <c r="T13" s="18">
-        <f>IF(AND(ISNUMBER(M13),M13&lt;0),M13*L13,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",L13&lt;&gt;"",IF(ISNUMBER(L13),AND(L13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L13&gt;0,N(I13)&gt;0)),MIN(0,L13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
       <c r="U13" s="18">
-        <f>IF(AND(ISNUMBER(O13),O13&lt;0),O13*N13,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",N13&lt;&gt;"",IF(ISNUMBER(N13),AND(N13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N13&gt;0,N(I13)&gt;0)),MIN(0,N13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
       <c r="V13" s="18">
-        <f>IF(AND(ISNUMBER(Q13),Q13&lt;0),Q13*P13,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",P13&lt;&gt;"",IF(ISNUMBER(P13),AND(P13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P13&gt;0,N(I13)&gt;0)),MIN(0,P13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
       <c r="W13" s="18">
-        <f>IF(AND(ISNUMBER(S13),S13&lt;0),S13*R13,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",R13&lt;&gt;"",IF(ISNUMBER(R13),AND(R13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R13&gt;0,N(I13)&gt;0)),MIN(0,R13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="F14" s="13">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(E14)),E14,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D14),AND(D14&gt;=0),FALSE)),"falta o material",E14/60*Config!$B$7+D14))))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(E14)),E14,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D14),AND(D14&gt;=0),FALSE)),"falta o material",E14/60*Config!$B$7+D14))))</f>
         <v/>
       </c>
       <c r="G14" s="14">
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF(OR(A14="",I14=""),"",IF(NOT(IF(ISNUMBER(I14),AND(I14&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A14="","",IF(I14="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I14),AND(I14&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F14)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"Margens inválidas",IF(I14=0,"Sem cobrança",IF(I14&lt;G14,"Abaixo do mínimo",IF(I14&lt;H14,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="L14" s="15" t="n"/>
@@ -1980,19 +1980,19 @@
         <v/>
       </c>
       <c r="T14" s="18">
-        <f>IF(AND(ISNUMBER(M14),M14&lt;0),M14*L14,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",L14&lt;&gt;"",IF(ISNUMBER(L14),AND(L14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L14&gt;0,N(I14)&gt;0)),MIN(0,L14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
       <c r="U14" s="18">
-        <f>IF(AND(ISNUMBER(O14),O14&lt;0),O14*N14,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",N14&lt;&gt;"",IF(ISNUMBER(N14),AND(N14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N14&gt;0,N(I14)&gt;0)),MIN(0,N14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
       <c r="V14" s="18">
-        <f>IF(AND(ISNUMBER(Q14),Q14&lt;0),Q14*P14,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",P14&lt;&gt;"",IF(ISNUMBER(P14),AND(P14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P14&gt;0,N(I14)&gt;0)),MIN(0,P14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
       <c r="W14" s="18">
-        <f>IF(AND(ISNUMBER(S14),S14&lt;0),S14*R14,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",R14&lt;&gt;"",IF(ISNUMBER(R14),AND(R14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R14&gt;0,N(I14)&gt;0)),MIN(0,R14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>IF(A15="","",IF(NOT(ISNUMBER(E15)),E15,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D15),AND(D15&gt;=0),FALSE)),"falta o material",E15/60*Config!$B$7+D15))))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(E15)),E15,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D15),AND(D15&gt;=0),FALSE)),"falta o material",E15/60*Config!$B$7+D15))))</f>
         <v/>
       </c>
       <c r="G15" s="14">
@@ -2023,7 +2023,7 @@
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF(OR(A15="",I15=""),"",IF(NOT(IF(ISNUMBER(I15),AND(I15&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A15="","",IF(I15="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I15),AND(I15&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F15)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"Margens inválidas",IF(I15=0,"Sem cobrança",IF(I15&lt;G15,"Abaixo do mínimo",IF(I15&lt;H15,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="L15" s="15" t="n"/>
@@ -2047,19 +2047,19 @@
         <v/>
       </c>
       <c r="T15" s="18">
-        <f>IF(AND(ISNUMBER(M15),M15&lt;0),M15*L15,0)</f>
+        <f>IF(AND(A15&lt;&gt;"",L15&lt;&gt;"",IF(ISNUMBER(L15),AND(L15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L15&gt;0,N(I15)&gt;0)),MIN(0,L15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
       <c r="U15" s="18">
-        <f>IF(AND(ISNUMBER(O15),O15&lt;0),O15*N15,0)</f>
+        <f>IF(AND(A15&lt;&gt;"",N15&lt;&gt;"",IF(ISNUMBER(N15),AND(N15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N15&gt;0,N(I15)&gt;0)),MIN(0,N15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
       <c r="V15" s="18">
-        <f>IF(AND(ISNUMBER(Q15),Q15&lt;0),Q15*P15,0)</f>
+        <f>IF(AND(A15&lt;&gt;"",P15&lt;&gt;"",IF(ISNUMBER(P15),AND(P15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P15&gt;0,N(I15)&gt;0)),MIN(0,P15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
       <c r="W15" s="18">
-        <f>IF(AND(ISNUMBER(S15),S15&lt;0),S15*R15,0)</f>
+        <f>IF(AND(A15&lt;&gt;"",R15&lt;&gt;"",IF(ISNUMBER(R15),AND(R15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R15&gt;0,N(I15)&gt;0)),MIN(0,R15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>IF(A16="","",IF(NOT(ISNUMBER(E16)),E16,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D16),AND(D16&gt;=0),FALSE)),"falta o material",E16/60*Config!$B$7+D16))))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(E16)),E16,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D16),AND(D16&gt;=0),FALSE)),"falta o material",E16/60*Config!$B$7+D16))))</f>
         <v/>
       </c>
       <c r="G16" s="14">
@@ -2090,7 +2090,7 @@
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF(OR(A16="",I16=""),"",IF(NOT(IF(ISNUMBER(I16),AND(I16&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A16="","",IF(I16="","Falta o preço particular",IF(NOT(IF(ISNUMBER(I16),AND(I16&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(F16)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"Margens inválidas",IF(I16=0,"Sem cobrança",IF(I16&lt;G16,"Abaixo do mínimo",IF(I16&lt;H16,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="L16" s="15" t="n"/>
@@ -2114,19 +2114,19 @@
         <v/>
       </c>
       <c r="T16" s="18">
-        <f>IF(AND(ISNUMBER(M16),M16&lt;0),M16*L16,0)</f>
+        <f>IF(AND(A16&lt;&gt;"",L16&lt;&gt;"",IF(ISNUMBER(L16),AND(L16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L16&gt;0,N(I16)&gt;0)),MIN(0,L16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
       <c r="U16" s="18">
-        <f>IF(AND(ISNUMBER(O16),O16&lt;0),O16*N16,0)</f>
+        <f>IF(AND(A16&lt;&gt;"",N16&lt;&gt;"",IF(ISNUMBER(N16),AND(N16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N16&gt;0,N(I16)&gt;0)),MIN(0,N16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
       <c r="V16" s="18">
-        <f>IF(AND(ISNUMBER(Q16),Q16&lt;0),Q16*P16,0)</f>
+        <f>IF(AND(A16&lt;&gt;"",P16&lt;&gt;"",IF(ISNUMBER(P16),AND(P16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P16&gt;0,N(I16)&gt;0)),MIN(0,P16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
       <c r="W16" s="18">
-        <f>IF(AND(ISNUMBER(S16),S16&lt;0),S16*R16,0)</f>
+        <f>IF(AND(A16&lt;&gt;"",R16&lt;&gt;"",IF(ISNUMBER(R16),AND(R16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R16&gt;0,N(I16)&gt;0)),MIN(0,R16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Retorno tem preço zero de propósito: o tempo dele já está no custo da consulta. Tabela de convênio abaixo do custo cheio não é automaticamente "não aceitar": com agenda vazia, o que importa é a contribuição (planilha 07).</t>
+          <t>Retorno tem preço zero de propósito: o tempo dele já está no custo da consulta. Tabela 0 em procedimento cobrado conta como prejuízo do custo cheio; no retorno (particular 0 também) não conta. Tabela de convênio abaixo do custo cheio não é automaticamente "não aceitar": com agenda vazia, o que importa é a contribuição (planilha 07).</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       <c r="C22" s="22" t="n"/>
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="14">
-        <f>IF(ISNUMBER(Config!$B$7),Config!$B$7,"falta o custo-hora em Config")</f>
+        <f>IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),Config!$B$7,"falta o custo-hora em Config")</f>
         <v>200</v>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="14">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",Config!$B$7/(1-Config!$B$8-Config!$B$9))))</f>
+        <f>IF(NOT(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",Config!$B$7/(1-Config!$B$8-Config!$B$9))))</f>
         <v>338.983050847458</v>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="24" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16))))</f>
+        <f>IF(NOT(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($K$5:$K$16,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$5:$A$16))))</f>
         <v>0 de 7</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="25">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($T$5:$W$16,"&lt;0"))))</f>
+        <f>IF(NOT(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($T$5:$W$16,"&lt;0"))))</f>
         <v>14</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="14">
-        <f>IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",-MIN($T$5:$W$16))))</f>
+        <f>IF(NOT(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE)),"falta o custo-hora em Config",IF((Config!$B$13&lt;&gt;"Sim"),"margens inválidas (Config)",IF((SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&gt;0,(SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*(ISNUMBER($F$5:$F$16)=FALSE))+SUMPRODUCT(($A$5:$A$16&lt;&gt;"")*($I$5:$I$16=""))+SUMPRODUCT(($A$5:$A$16="")*(($B$5:$B$16&lt;&gt;"")+($C$5:$C$16&lt;&gt;"")+($D$5:$D$16&lt;&gt;"")+($I$5:$I$16&lt;&gt;"")+($L$5:$L$16&lt;&gt;"")+($N$5:$N$16&lt;&gt;"")+($P$5:$P$16&lt;&gt;"")+($R$5:$R$16&lt;&gt;"")&gt;0))+SUMPRODUCT(ISTEXT($I$5:$I$16)+ISNUMBER($I$5:$I$16)*($I$5:$I$16&lt;0))+SUMPRODUCT(ISTEXT($L$5:$L$16)+ISNUMBER($L$5:$L$16)*($L$5:$L$16&lt;0))+SUMPRODUCT(ISTEXT($N$5:$N$16)+ISNUMBER($N$5:$N$16)*($N$5:$N$16&lt;0))+SUMPRODUCT(ISTEXT($P$5:$P$16)+ISNUMBER($P$5:$P$16)*($P$5:$P$16&lt;0))+SUMPRODUCT(ISTEXT($R$5:$R$16)+ISNUMBER($R$5:$R$16)*($R$5:$R$16&lt;0)))&amp;" linha(s) ou preço(s) incompletos",-MIN($T$5:$W$16))))</f>
         <v>60.4333333333333</v>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="B36" s="27">
-        <f>IF(NOT(ISNUMBER(B35)),B35,IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(B33),AND(B33&gt;=0),FALSE)),"falta o material",B35/60*Config!$B$7+B33)))</f>
+        <f>IF(NOT(ISNUMBER(B35)),B35,IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(B33),AND(B33&gt;=0),FALSE)),"falta o material",B35/60*Config!$B$7+B33)))</f>
         <v>180.666666666667</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B40" s="28" t="str">
-        <f>IF(B34="","",IF(NOT(IF(ISNUMBER(B34),AND(B34&gt;=0),FALSE)),"Preço pretendido inválido",IF(B34=0,"",IF(NOT(ISNUMBER(B36)),IF(ISNUMBER(Config!$B$7),"Faltam dados: "&amp;B36,"Falta o custo-hora em Config"),IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))))</f>
+        <f>IF(B34="","",IF(NOT(IF(ISNUMBER(B34),AND(B34&gt;=0),FALSE)),"Preço pretendido inválido",IF(B34=0,"",IF(NOT(ISNUMBER(B36)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados: "&amp;B36,"Falta o custo-hora em Config"),IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(B38))),"Margens inválidas em Config",IF(B34&lt;B37,"Abaixo do mínimo: cobre parte do custo, não a margem",IF(B34&lt;B38,"Entre o mínimo e o alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="C40" s="22" t="n"/>
@@ -2381,7 +2381,7 @@
   </mergeCells>
   <conditionalFormatting sqref="K5:K16">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(K5="Abaixo do mínimo",K5="Falta o custo-hora",K5="Margens inválidas",K5="Faltam dados da linha",K5="Preço inválido")</formula>
+      <formula>OR(K5="Abaixo do mínimo",K5="Falta o custo-hora",K5="Margens inválidas",K5="Faltam dados da linha",K5="Preço inválido",K5="Falta o preço particular")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>K5="Entre mínimo e alvo"</formula>
@@ -2673,7 +2673,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
       <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1),FALSE)</formula1>
     </dataValidation>
@@ -2683,6 +2683,9 @@
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
       <formula1>=IF(ISNUMBER(B10),AND(B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1),FALSE)</formula1>
     </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Custo-hora" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/06-precificacao.xlsx
@@ -1261,19 +1261,19 @@
         <v/>
       </c>
       <c r="T5" s="18">
-        <f>IF(AND(A5&lt;&gt;"",L5&lt;&gt;"",IF(ISNUMBER(L5),AND(L5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L5&gt;0,N(I5)&gt;0)),MIN(0,L5*(1-Config!$B$8)-F5),0)</f>
+        <f>IF(AND(A5&lt;&gt;"",L5&lt;&gt;"",IF(ISNUMBER(L5),AND(L5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L5&gt;0,TRIM(A5)&lt;&gt;"Retorno")),MIN(0,L5*(1-Config!$B$8)-F5),0)</f>
         <v>-23.8666666666667</v>
       </c>
       <c r="U5" s="18">
-        <f>IF(AND(A5&lt;&gt;"",N5&lt;&gt;"",IF(ISNUMBER(N5),AND(N5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N5&gt;0,N(I5)&gt;0)),MIN(0,N5*(1-Config!$B$8)-F5),0)</f>
+        <f>IF(AND(A5&lt;&gt;"",N5&lt;&gt;"",IF(ISNUMBER(N5),AND(N5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N5&gt;0,TRIM(A5)&lt;&gt;"Retorno")),MIN(0,N5*(1-Config!$B$8)-F5),0)</f>
         <v>-41.6666666666667</v>
       </c>
       <c r="V5" s="18">
-        <f>IF(AND(A5&lt;&gt;"",P5&lt;&gt;"",IF(ISNUMBER(P5),AND(P5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P5&gt;0,N(I5)&gt;0)),MIN(0,P5*(1-Config!$B$8)-F5),0)</f>
+        <f>IF(AND(A5&lt;&gt;"",P5&lt;&gt;"",IF(ISNUMBER(P5),AND(P5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P5&gt;0,TRIM(A5)&lt;&gt;"Retorno")),MIN(0,P5*(1-Config!$B$8)-F5),0)</f>
         <v>-50.5666666666667</v>
       </c>
       <c r="W5" s="18">
-        <f>IF(AND(A5&lt;&gt;"",R5&lt;&gt;"",IF(ISNUMBER(R5),AND(R5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R5&gt;0,N(I5)&gt;0)),MIN(0,R5*(1-Config!$B$8)-F5),0)</f>
+        <f>IF(AND(A5&lt;&gt;"",R5&lt;&gt;"",IF(ISNUMBER(R5),AND(R5&gt;=0),FALSE),ISNUMBER(F5),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R5&gt;0,TRIM(A5)&lt;&gt;"Retorno")),MIN(0,R5*(1-Config!$B$8)-F5),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1348,19 +1348,19 @@
         <v/>
       </c>
       <c r="T6" s="18">
-        <f>IF(AND(A6&lt;&gt;"",L6&lt;&gt;"",IF(ISNUMBER(L6),AND(L6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L6&gt;0,N(I6)&gt;0)),MIN(0,L6*(1-Config!$B$8)-F6),0)</f>
+        <f>IF(AND(A6&lt;&gt;"",L6&lt;&gt;"",IF(ISNUMBER(L6),AND(L6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L6&gt;0,TRIM(A6)&lt;&gt;"Retorno")),MIN(0,L6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
       <c r="U6" s="18">
-        <f>IF(AND(A6&lt;&gt;"",N6&lt;&gt;"",IF(ISNUMBER(N6),AND(N6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N6&gt;0,N(I6)&gt;0)),MIN(0,N6*(1-Config!$B$8)-F6),0)</f>
+        <f>IF(AND(A6&lt;&gt;"",N6&lt;&gt;"",IF(ISNUMBER(N6),AND(N6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N6&gt;0,TRIM(A6)&lt;&gt;"Retorno")),MIN(0,N6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
       <c r="V6" s="18">
-        <f>IF(AND(A6&lt;&gt;"",P6&lt;&gt;"",IF(ISNUMBER(P6),AND(P6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P6&gt;0,N(I6)&gt;0)),MIN(0,P6*(1-Config!$B$8)-F6),0)</f>
+        <f>IF(AND(A6&lt;&gt;"",P6&lt;&gt;"",IF(ISNUMBER(P6),AND(P6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P6&gt;0,TRIM(A6)&lt;&gt;"Retorno")),MIN(0,P6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="18">
-        <f>IF(AND(A6&lt;&gt;"",R6&lt;&gt;"",IF(ISNUMBER(R6),AND(R6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R6&gt;0,N(I6)&gt;0)),MIN(0,R6*(1-Config!$B$8)-F6),0)</f>
+        <f>IF(AND(A6&lt;&gt;"",R6&lt;&gt;"",IF(ISNUMBER(R6),AND(R6&gt;=0),FALSE),ISNUMBER(F6),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R6&gt;0,TRIM(A6)&lt;&gt;"Retorno")),MIN(0,R6*(1-Config!$B$8)-F6),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1435,19 +1435,19 @@
         <v/>
       </c>
       <c r="T7" s="18">
-        <f>IF(AND(A7&lt;&gt;"",L7&lt;&gt;"",IF(ISNUMBER(L7),AND(L7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L7&gt;0,N(I7)&gt;0)),MIN(0,L7*(1-Config!$B$8)-F7),0)</f>
+        <f>IF(AND(A7&lt;&gt;"",L7&lt;&gt;"",IF(ISNUMBER(L7),AND(L7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L7&gt;0,TRIM(A7)&lt;&gt;"Retorno")),MIN(0,L7*(1-Config!$B$8)-F7),0)</f>
         <v>-39.0666666666667</v>
       </c>
       <c r="U7" s="18">
-        <f>IF(AND(A7&lt;&gt;"",N7&lt;&gt;"",IF(ISNUMBER(N7),AND(N7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N7&gt;0,N(I7)&gt;0)),MIN(0,N7*(1-Config!$B$8)-F7),0)</f>
+        <f>IF(AND(A7&lt;&gt;"",N7&lt;&gt;"",IF(ISNUMBER(N7),AND(N7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N7&gt;0,TRIM(A7)&lt;&gt;"Retorno")),MIN(0,N7*(1-Config!$B$8)-F7),0)</f>
         <v>-43.5166666666667</v>
       </c>
       <c r="V7" s="18">
-        <f>IF(AND(A7&lt;&gt;"",P7&lt;&gt;"",IF(ISNUMBER(P7),AND(P7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P7&gt;0,N(I7)&gt;0)),MIN(0,P7*(1-Config!$B$8)-F7),0)</f>
+        <f>IF(AND(A7&lt;&gt;"",P7&lt;&gt;"",IF(ISNUMBER(P7),AND(P7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P7&gt;0,TRIM(A7)&lt;&gt;"Retorno")),MIN(0,P7*(1-Config!$B$8)-F7),0)</f>
         <v>-46.1866666666667</v>
       </c>
       <c r="W7" s="18">
-        <f>IF(AND(A7&lt;&gt;"",R7&lt;&gt;"",IF(ISNUMBER(R7),AND(R7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R7&gt;0,N(I7)&gt;0)),MIN(0,R7*(1-Config!$B$8)-F7),0)</f>
+        <f>IF(AND(A7&lt;&gt;"",R7&lt;&gt;"",IF(ISNUMBER(R7),AND(R7&gt;=0),FALSE),ISNUMBER(F7),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R7&gt;0,TRIM(A7)&lt;&gt;"Retorno")),MIN(0,R7*(1-Config!$B$8)-F7),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1522,19 +1522,19 @@
         <v/>
       </c>
       <c r="T8" s="18">
-        <f>IF(AND(A8&lt;&gt;"",L8&lt;&gt;"",IF(ISNUMBER(L8),AND(L8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L8&gt;0,N(I8)&gt;0)),MIN(0,L8*(1-Config!$B$8)-F8),0)</f>
+        <f>IF(AND(A8&lt;&gt;"",L8&lt;&gt;"",IF(ISNUMBER(L8),AND(L8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L8&gt;0,TRIM(A8)&lt;&gt;"Retorno")),MIN(0,L8*(1-Config!$B$8)-F8),0)</f>
         <v>0</v>
       </c>
       <c r="U8" s="18">
-        <f>IF(AND(A8&lt;&gt;"",N8&lt;&gt;"",IF(ISNUMBER(N8),AND(N8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N8&gt;0,N(I8)&gt;0)),MIN(0,N8*(1-Config!$B$8)-F8),0)</f>
+        <f>IF(AND(A8&lt;&gt;"",N8&lt;&gt;"",IF(ISNUMBER(N8),AND(N8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N8&gt;0,TRIM(A8)&lt;&gt;"Retorno")),MIN(0,N8*(1-Config!$B$8)-F8),0)</f>
         <v>-6.01666666666665</v>
       </c>
       <c r="V8" s="18">
-        <f>IF(AND(A8&lt;&gt;"",P8&lt;&gt;"",IF(ISNUMBER(P8),AND(P8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P8&gt;0,N(I8)&gt;0)),MIN(0,P8*(1-Config!$B$8)-F8),0)</f>
+        <f>IF(AND(A8&lt;&gt;"",P8&lt;&gt;"",IF(ISNUMBER(P8),AND(P8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P8&gt;0,TRIM(A8)&lt;&gt;"Retorno")),MIN(0,P8*(1-Config!$B$8)-F8),0)</f>
         <v>-14.9166666666667</v>
       </c>
       <c r="W8" s="18">
-        <f>IF(AND(A8&lt;&gt;"",R8&lt;&gt;"",IF(ISNUMBER(R8),AND(R8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R8&gt;0,N(I8)&gt;0)),MIN(0,R8*(1-Config!$B$8)-F8),0)</f>
+        <f>IF(AND(A8&lt;&gt;"",R8&lt;&gt;"",IF(ISNUMBER(R8),AND(R8&gt;=0),FALSE),ISNUMBER(F8),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R8&gt;0,TRIM(A8)&lt;&gt;"Retorno")),MIN(0,R8*(1-Config!$B$8)-F8),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1609,19 +1609,19 @@
         <v/>
       </c>
       <c r="T9" s="18">
-        <f>IF(AND(A9&lt;&gt;"",L9&lt;&gt;"",IF(ISNUMBER(L9),AND(L9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L9&gt;0,N(I9)&gt;0)),MIN(0,L9*(1-Config!$B$8)-F9),0)</f>
+        <f>IF(AND(A9&lt;&gt;"",L9&lt;&gt;"",IF(ISNUMBER(L9),AND(L9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L9&gt;0,TRIM(A9)&lt;&gt;"Retorno")),MIN(0,L9*(1-Config!$B$8)-F9),0)</f>
         <v>0</v>
       </c>
       <c r="U9" s="18">
-        <f>IF(AND(A9&lt;&gt;"",N9&lt;&gt;"",IF(ISNUMBER(N9),AND(N9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N9&gt;0,N(I9)&gt;0)),MIN(0,N9*(1-Config!$B$8)-F9),0)</f>
+        <f>IF(AND(A9&lt;&gt;"",N9&lt;&gt;"",IF(ISNUMBER(N9),AND(N9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N9&gt;0,TRIM(A9)&lt;&gt;"Retorno")),MIN(0,N9*(1-Config!$B$8)-F9),0)</f>
         <v>-0.11666666666666</v>
       </c>
       <c r="V9" s="18">
-        <f>IF(AND(A9&lt;&gt;"",P9&lt;&gt;"",IF(ISNUMBER(P9),AND(P9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P9&gt;0,N(I9)&gt;0)),MIN(0,P9*(1-Config!$B$8)-F9),0)</f>
+        <f>IF(AND(A9&lt;&gt;"",P9&lt;&gt;"",IF(ISNUMBER(P9),AND(P9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P9&gt;0,TRIM(A9)&lt;&gt;"Retorno")),MIN(0,P9*(1-Config!$B$8)-F9),0)</f>
         <v>-9.01666666666665</v>
       </c>
       <c r="W9" s="18">
-        <f>IF(AND(A9&lt;&gt;"",R9&lt;&gt;"",IF(ISNUMBER(R9),AND(R9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R9&gt;0,N(I9)&gt;0)),MIN(0,R9*(1-Config!$B$8)-F9),0)</f>
+        <f>IF(AND(A9&lt;&gt;"",R9&lt;&gt;"",IF(ISNUMBER(R9),AND(R9&gt;=0),FALSE),ISNUMBER(F9),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R9&gt;0,TRIM(A9)&lt;&gt;"Retorno")),MIN(0,R9*(1-Config!$B$8)-F9),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1696,19 +1696,19 @@
         <v/>
       </c>
       <c r="T10" s="18">
-        <f>IF(AND(A10&lt;&gt;"",L10&lt;&gt;"",IF(ISNUMBER(L10),AND(L10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L10&gt;0,N(I10)&gt;0)),MIN(0,L10*(1-Config!$B$8)-F10),0)</f>
+        <f>IF(AND(A10&lt;&gt;"",L10&lt;&gt;"",IF(ISNUMBER(L10),AND(L10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L10&gt;0,TRIM(A10)&lt;&gt;"Retorno")),MIN(0,L10*(1-Config!$B$8)-F10),0)</f>
         <v>-33.7333333333333</v>
       </c>
       <c r="U10" s="18">
-        <f>IF(AND(A10&lt;&gt;"",N10&lt;&gt;"",IF(ISNUMBER(N10),AND(N10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N10&gt;0,N(I10)&gt;0)),MIN(0,N10*(1-Config!$B$8)-F10),0)</f>
+        <f>IF(AND(A10&lt;&gt;"",N10&lt;&gt;"",IF(ISNUMBER(N10),AND(N10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N10&gt;0,TRIM(A10)&lt;&gt;"Retorno")),MIN(0,N10*(1-Config!$B$8)-F10),0)</f>
         <v>-47.0833333333333</v>
       </c>
       <c r="V10" s="18">
-        <f>IF(AND(A10&lt;&gt;"",P10&lt;&gt;"",IF(ISNUMBER(P10),AND(P10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P10&gt;0,N(I10)&gt;0)),MIN(0,P10*(1-Config!$B$8)-F10),0)</f>
+        <f>IF(AND(A10&lt;&gt;"",P10&lt;&gt;"",IF(ISNUMBER(P10),AND(P10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P10&gt;0,TRIM(A10)&lt;&gt;"Retorno")),MIN(0,P10*(1-Config!$B$8)-F10),0)</f>
         <v>-60.4333333333333</v>
       </c>
       <c r="W10" s="18">
-        <f>IF(AND(A10&lt;&gt;"",R10&lt;&gt;"",IF(ISNUMBER(R10),AND(R10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R10&gt;0,N(I10)&gt;0)),MIN(0,R10*(1-Config!$B$8)-F10),0)</f>
+        <f>IF(AND(A10&lt;&gt;"",R10&lt;&gt;"",IF(ISNUMBER(R10),AND(R10&gt;=0),FALSE),ISNUMBER(F10),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R10&gt;0,TRIM(A10)&lt;&gt;"Retorno")),MIN(0,R10*(1-Config!$B$8)-F10),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1779,19 +1779,19 @@
         <v/>
       </c>
       <c r="T11" s="18">
-        <f>IF(AND(A11&lt;&gt;"",L11&lt;&gt;"",IF(ISNUMBER(L11),AND(L11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L11&gt;0,N(I11)&gt;0)),MIN(0,L11*(1-Config!$B$8)-F11),0)</f>
+        <f>IF(AND(A11&lt;&gt;"",L11&lt;&gt;"",IF(ISNUMBER(L11),AND(L11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L11&gt;0,TRIM(A11)&lt;&gt;"Retorno")),MIN(0,L11*(1-Config!$B$8)-F11),0)</f>
         <v>-48.3</v>
       </c>
       <c r="U11" s="18">
-        <f>IF(AND(A11&lt;&gt;"",N11&lt;&gt;"",IF(ISNUMBER(N11),AND(N11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N11&gt;0,N(I11)&gt;0)),MIN(0,N11*(1-Config!$B$8)-F11),0)</f>
+        <f>IF(AND(A11&lt;&gt;"",N11&lt;&gt;"",IF(ISNUMBER(N11),AND(N11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N11&gt;0,TRIM(A11)&lt;&gt;"Retorno")),MIN(0,N11*(1-Config!$B$8)-F11),0)</f>
         <v>0</v>
       </c>
       <c r="V11" s="18">
-        <f>IF(AND(A11&lt;&gt;"",P11&lt;&gt;"",IF(ISNUMBER(P11),AND(P11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P11&gt;0,N(I11)&gt;0)),MIN(0,P11*(1-Config!$B$8)-F11),0)</f>
+        <f>IF(AND(A11&lt;&gt;"",P11&lt;&gt;"",IF(ISNUMBER(P11),AND(P11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P11&gt;0,TRIM(A11)&lt;&gt;"Retorno")),MIN(0,P11*(1-Config!$B$8)-F11),0)</f>
         <v>0</v>
       </c>
       <c r="W11" s="18">
-        <f>IF(AND(A11&lt;&gt;"",R11&lt;&gt;"",IF(ISNUMBER(R11),AND(R11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R11&gt;0,N(I11)&gt;0)),MIN(0,R11*(1-Config!$B$8)-F11),0)</f>
+        <f>IF(AND(A11&lt;&gt;"",R11&lt;&gt;"",IF(ISNUMBER(R11),AND(R11&gt;=0),FALSE),ISNUMBER(F11),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R11&gt;0,TRIM(A11)&lt;&gt;"Retorno")),MIN(0,R11*(1-Config!$B$8)-F11),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1846,19 +1846,19 @@
         <v/>
       </c>
       <c r="T12" s="18">
-        <f>IF(AND(A12&lt;&gt;"",L12&lt;&gt;"",IF(ISNUMBER(L12),AND(L12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L12&gt;0,N(I12)&gt;0)),MIN(0,L12*(1-Config!$B$8)-F12),0)</f>
+        <f>IF(AND(A12&lt;&gt;"",L12&lt;&gt;"",IF(ISNUMBER(L12),AND(L12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L12&gt;0,TRIM(A12)&lt;&gt;"Retorno")),MIN(0,L12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
       <c r="U12" s="18">
-        <f>IF(AND(A12&lt;&gt;"",N12&lt;&gt;"",IF(ISNUMBER(N12),AND(N12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N12&gt;0,N(I12)&gt;0)),MIN(0,N12*(1-Config!$B$8)-F12),0)</f>
+        <f>IF(AND(A12&lt;&gt;"",N12&lt;&gt;"",IF(ISNUMBER(N12),AND(N12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N12&gt;0,TRIM(A12)&lt;&gt;"Retorno")),MIN(0,N12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
       <c r="V12" s="18">
-        <f>IF(AND(A12&lt;&gt;"",P12&lt;&gt;"",IF(ISNUMBER(P12),AND(P12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P12&gt;0,N(I12)&gt;0)),MIN(0,P12*(1-Config!$B$8)-F12),0)</f>
+        <f>IF(AND(A12&lt;&gt;"",P12&lt;&gt;"",IF(ISNUMBER(P12),AND(P12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P12&gt;0,TRIM(A12)&lt;&gt;"Retorno")),MIN(0,P12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
       <c r="W12" s="18">
-        <f>IF(AND(A12&lt;&gt;"",R12&lt;&gt;"",IF(ISNUMBER(R12),AND(R12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R12&gt;0,N(I12)&gt;0)),MIN(0,R12*(1-Config!$B$8)-F12),0)</f>
+        <f>IF(AND(A12&lt;&gt;"",R12&lt;&gt;"",IF(ISNUMBER(R12),AND(R12&gt;=0),FALSE),ISNUMBER(F12),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R12&gt;0,TRIM(A12)&lt;&gt;"Retorno")),MIN(0,R12*(1-Config!$B$8)-F12),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1913,19 +1913,19 @@
         <v/>
       </c>
       <c r="T13" s="18">
-        <f>IF(AND(A13&lt;&gt;"",L13&lt;&gt;"",IF(ISNUMBER(L13),AND(L13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L13&gt;0,N(I13)&gt;0)),MIN(0,L13*(1-Config!$B$8)-F13),0)</f>
+        <f>IF(AND(A13&lt;&gt;"",L13&lt;&gt;"",IF(ISNUMBER(L13),AND(L13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L13&gt;0,TRIM(A13)&lt;&gt;"Retorno")),MIN(0,L13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
       <c r="U13" s="18">
-        <f>IF(AND(A13&lt;&gt;"",N13&lt;&gt;"",IF(ISNUMBER(N13),AND(N13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N13&gt;0,N(I13)&gt;0)),MIN(0,N13*(1-Config!$B$8)-F13),0)</f>
+        <f>IF(AND(A13&lt;&gt;"",N13&lt;&gt;"",IF(ISNUMBER(N13),AND(N13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N13&gt;0,TRIM(A13)&lt;&gt;"Retorno")),MIN(0,N13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
       <c r="V13" s="18">
-        <f>IF(AND(A13&lt;&gt;"",P13&lt;&gt;"",IF(ISNUMBER(P13),AND(P13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P13&gt;0,N(I13)&gt;0)),MIN(0,P13*(1-Config!$B$8)-F13),0)</f>
+        <f>IF(AND(A13&lt;&gt;"",P13&lt;&gt;"",IF(ISNUMBER(P13),AND(P13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P13&gt;0,TRIM(A13)&lt;&gt;"Retorno")),MIN(0,P13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
       <c r="W13" s="18">
-        <f>IF(AND(A13&lt;&gt;"",R13&lt;&gt;"",IF(ISNUMBER(R13),AND(R13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R13&gt;0,N(I13)&gt;0)),MIN(0,R13*(1-Config!$B$8)-F13),0)</f>
+        <f>IF(AND(A13&lt;&gt;"",R13&lt;&gt;"",IF(ISNUMBER(R13),AND(R13&gt;=0),FALSE),ISNUMBER(F13),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R13&gt;0,TRIM(A13)&lt;&gt;"Retorno")),MIN(0,R13*(1-Config!$B$8)-F13),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1980,19 +1980,19 @@
         <v/>
       </c>
       <c r="T14" s="18">
-        <f>IF(AND(A14&lt;&gt;"",L14&lt;&gt;"",IF(ISNUMBER(L14),AND(L14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L14&gt;0,N(I14)&gt;0)),MIN(0,L14*(1-Config!$B$8)-F14),0)</f>
+        <f>IF(AND(A14&lt;&gt;"",L14&lt;&gt;"",IF(ISNUMBER(L14),AND(L14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L14&gt;0,TRIM(A14)&lt;&gt;"Retorno")),MIN(0,L14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
       <c r="U14" s="18">
-        <f>IF(AND(A14&lt;&gt;"",N14&lt;&gt;"",IF(ISNUMBER(N14),AND(N14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N14&gt;0,N(I14)&gt;0)),MIN(0,N14*(1-Config!$B$8)-F14),0)</f>
+        <f>IF(AND(A14&lt;&gt;"",N14&lt;&gt;"",IF(ISNUMBER(N14),AND(N14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N14&gt;0,TRIM(A14)&lt;&gt;"Retorno")),MIN(0,N14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
       <c r="V14" s="18">
-        <f>IF(AND(A14&lt;&gt;"",P14&lt;&gt;"",IF(ISNUMBER(P14),AND(P14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P14&gt;0,N(I14)&gt;0)),MIN(0,P14*(1-Config!$B$8)-F14),0)</f>
+        <f>IF(AND(A14&lt;&gt;"",P14&lt;&gt;"",IF(ISNUMBER(P14),AND(P14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P14&gt;0,TRIM(A14)&lt;&gt;"Retorno")),MIN(0,P14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
       <c r="W14" s="18">
-        <f>IF(AND(A14&lt;&gt;"",R14&lt;&gt;"",IF(ISNUMBER(R14),AND(R14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R14&gt;0,N(I14)&gt;0)),MIN(0,R14*(1-Config!$B$8)-F14),0)</f>
+        <f>IF(AND(A14&lt;&gt;"",R14&lt;&gt;"",IF(ISNUMBER(R14),AND(R14&gt;=0),FALSE),ISNUMBER(F14),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R14&gt;0,TRIM(A14)&lt;&gt;"Retorno")),MIN(0,R14*(1-Config!$B$8)-F14),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2047,19 +2047,19 @@
         <v/>
       </c>
       <c r="T15" s="18">
-        <f>IF(AND(A15&lt;&gt;"",L15&lt;&gt;"",IF(ISNUMBER(L15),AND(L15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L15&gt;0,N(I15)&gt;0)),MIN(0,L15*(1-Config!$B$8)-F15),0)</f>
+        <f>IF(AND(A15&lt;&gt;"",L15&lt;&gt;"",IF(ISNUMBER(L15),AND(L15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L15&gt;0,TRIM(A15)&lt;&gt;"Retorno")),MIN(0,L15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
       <c r="U15" s="18">
-        <f>IF(AND(A15&lt;&gt;"",N15&lt;&gt;"",IF(ISNUMBER(N15),AND(N15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N15&gt;0,N(I15)&gt;0)),MIN(0,N15*(1-Config!$B$8)-F15),0)</f>
+        <f>IF(AND(A15&lt;&gt;"",N15&lt;&gt;"",IF(ISNUMBER(N15),AND(N15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N15&gt;0,TRIM(A15)&lt;&gt;"Retorno")),MIN(0,N15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
       <c r="V15" s="18">
-        <f>IF(AND(A15&lt;&gt;"",P15&lt;&gt;"",IF(ISNUMBER(P15),AND(P15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P15&gt;0,N(I15)&gt;0)),MIN(0,P15*(1-Config!$B$8)-F15),0)</f>
+        <f>IF(AND(A15&lt;&gt;"",P15&lt;&gt;"",IF(ISNUMBER(P15),AND(P15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P15&gt;0,TRIM(A15)&lt;&gt;"Retorno")),MIN(0,P15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
       <c r="W15" s="18">
-        <f>IF(AND(A15&lt;&gt;"",R15&lt;&gt;"",IF(ISNUMBER(R15),AND(R15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R15&gt;0,N(I15)&gt;0)),MIN(0,R15*(1-Config!$B$8)-F15),0)</f>
+        <f>IF(AND(A15&lt;&gt;"",R15&lt;&gt;"",IF(ISNUMBER(R15),AND(R15&gt;=0),FALSE),ISNUMBER(F15),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R15&gt;0,TRIM(A15)&lt;&gt;"Retorno")),MIN(0,R15*(1-Config!$B$8)-F15),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2114,19 +2114,19 @@
         <v/>
       </c>
       <c r="T16" s="18">
-        <f>IF(AND(A16&lt;&gt;"",L16&lt;&gt;"",IF(ISNUMBER(L16),AND(L16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L16&gt;0,N(I16)&gt;0)),MIN(0,L16*(1-Config!$B$8)-F16),0)</f>
+        <f>IF(AND(A16&lt;&gt;"",L16&lt;&gt;"",IF(ISNUMBER(L16),AND(L16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(L16&gt;0,TRIM(A16)&lt;&gt;"Retorno")),MIN(0,L16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
       <c r="U16" s="18">
-        <f>IF(AND(A16&lt;&gt;"",N16&lt;&gt;"",IF(ISNUMBER(N16),AND(N16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N16&gt;0,N(I16)&gt;0)),MIN(0,N16*(1-Config!$B$8)-F16),0)</f>
+        <f>IF(AND(A16&lt;&gt;"",N16&lt;&gt;"",IF(ISNUMBER(N16),AND(N16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(N16&gt;0,TRIM(A16)&lt;&gt;"Retorno")),MIN(0,N16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
       <c r="V16" s="18">
-        <f>IF(AND(A16&lt;&gt;"",P16&lt;&gt;"",IF(ISNUMBER(P16),AND(P16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P16&gt;0,N(I16)&gt;0)),MIN(0,P16*(1-Config!$B$8)-F16),0)</f>
+        <f>IF(AND(A16&lt;&gt;"",P16&lt;&gt;"",IF(ISNUMBER(P16),AND(P16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(P16&gt;0,TRIM(A16)&lt;&gt;"Retorno")),MIN(0,P16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
       <c r="W16" s="18">
-        <f>IF(AND(A16&lt;&gt;"",R16&lt;&gt;"",IF(ISNUMBER(R16),AND(R16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R16&gt;0,N(I16)&gt;0)),MIN(0,R16*(1-Config!$B$8)-F16),0)</f>
+        <f>IF(AND(A16&lt;&gt;"",R16&lt;&gt;"",IF(ISNUMBER(R16),AND(R16&gt;=0),FALSE),ISNUMBER(F16),NOT((Config!$B$13&lt;&gt;"Sim")),OR(R16&gt;0,TRIM(A16)&lt;&gt;"Retorno")),MIN(0,R16*(1-Config!$B$8)-F16),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Retorno tem preço zero de propósito: o tempo dele já está no custo da consulta. Tabela 0 em procedimento cobrado conta como prejuízo do custo cheio; no retorno (particular 0 também) não conta. Tabela de convênio abaixo do custo cheio não é automaticamente "não aceitar": com agenda vazia, o que importa é a contribuição (planilha 07).</t>
+          <t>Retorno tem preço zero de propósito: o tempo dele já está no custo da consulta. Tabela 0 conta como prejuízo do custo cheio em qualquer procedimento, inclusive sem cobrança no particular; só não conta na linha chamada Retorno, cujo tempo já está no custo da consulta. Tabela de convênio abaixo do custo cheio não é automaticamente "não aceitar": com agenda vazia, o que importa é a contribuição (planilha 07).</t>
         </is>
       </c>
     </row>
@@ -2390,58 +2390,78 @@
       <formula>K5="No alvo ou acima"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L16">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>IF(ISNUMBER(L5),AND(L5=0,TRIM($A5)&lt;&gt;"Retorno",ISNUMBER($F5),NOT((INDIRECT("Config!$B$13")&lt;&gt;"Sim"))),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N16">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>IF(ISNUMBER(N5),AND(N5=0,TRIM($A5)&lt;&gt;"Retorno",ISNUMBER($F5),NOT((INDIRECT("Config!$B$13")&lt;&gt;"Sim"))),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5:P16">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>IF(ISNUMBER(P5),AND(P5=0,TRIM($A5)&lt;&gt;"Retorno",ISNUMBER($F5),NOT((INDIRECT("Config!$B$13")&lt;&gt;"Sim"))),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:R16">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>IF(ISNUMBER(R5),AND(R5=0,TRIM($A5)&lt;&gt;"Retorno",ISNUMBER($F5),NOT((INDIRECT("Config!$B$13")&lt;&gt;"Sim"))),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J5:J16">
-    <cfRule type="expression" priority="4" dxfId="0">
+    <cfRule type="expression" priority="8" dxfId="0">
       <formula>AND(ISNUMBER(J5),J5&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="9" dxfId="1">
       <formula>AND(ISNUMBER(J5),J5&gt;=0,J5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="2">
       <formula>AND(ISNUMBER(J5),J5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M16">
-    <cfRule type="expression" priority="7" dxfId="0">
+    <cfRule type="expression" priority="11" dxfId="0">
       <formula>AND(ISNUMBER(M5),M5&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="1">
+    <cfRule type="expression" priority="12" dxfId="1">
       <formula>AND(ISNUMBER(M5),M5&gt;=0,M5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="2">
+    <cfRule type="expression" priority="13" dxfId="2">
       <formula>AND(ISNUMBER(M5),M5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O16">
-    <cfRule type="expression" priority="10" dxfId="0">
+    <cfRule type="expression" priority="14" dxfId="0">
       <formula>AND(ISNUMBER(O5),O5&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" dxfId="1">
+    <cfRule type="expression" priority="15" dxfId="1">
       <formula>AND(ISNUMBER(O5),O5&gt;=0,O5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="2">
+    <cfRule type="expression" priority="16" dxfId="2">
       <formula>AND(ISNUMBER(O5),O5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q16">
-    <cfRule type="expression" priority="13" dxfId="0">
+    <cfRule type="expression" priority="17" dxfId="0">
       <formula>AND(ISNUMBER(Q5),Q5&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="1">
+    <cfRule type="expression" priority="18" dxfId="1">
       <formula>AND(ISNUMBER(Q5),Q5&gt;=0,Q5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" dxfId="2">
+    <cfRule type="expression" priority="19" dxfId="2">
       <formula>AND(ISNUMBER(Q5),Q5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S16">
-    <cfRule type="expression" priority="16" dxfId="0">
+    <cfRule type="expression" priority="20" dxfId="0">
       <formula>AND(ISNUMBER(S5),S5&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" dxfId="1">
+    <cfRule type="expression" priority="21" dxfId="1">
       <formula>AND(ISNUMBER(S5),S5&gt;=0,S5&lt;INDIRECT("Config!$B$9"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" dxfId="2">
+    <cfRule type="expression" priority="22" dxfId="2">
       <formula>AND(ISNUMBER(S5),S5&gt;=INDIRECT("Config!$B$9"))</formula>
     </cfRule>
   </conditionalFormatting>
